--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,397 +656,409 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3459000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3826000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4269000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3178000</v>
       </c>
-      <c r="G8" s="3">
-        <v>3318000</v>
-      </c>
       <c r="H8" s="3">
+        <v>4261000</v>
+      </c>
+      <c r="I8" s="3">
         <v>3284000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2018000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3454000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3853000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3800000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4144000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3698000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4186000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3312000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3519000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3221000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3365000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3531000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6735000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3344000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3136000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3093000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3012000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1651000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1703000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1571000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1577000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1576000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1500000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1395000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1305000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1559000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1461000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1492000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1534000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1612000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1441000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1682000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1345000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3431000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1490000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2372000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3028000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1465000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1376000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1021000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1455000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>876000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1808000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2123000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2698000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1601000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1742000</v>
-      </c>
       <c r="H10" s="3">
+        <v>2761000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1889000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>713000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1895000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2392000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2308000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2610000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2086000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2745000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1630000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2174000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-210000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1875000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1159000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3707000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1879000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1760000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2072000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1557000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1079,8 +1091,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1171,8 +1184,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1279,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1296,67 +1315,70 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-5000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>58000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>31000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>38000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>7000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>25800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>27200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>35000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>24300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1447,8 +1469,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1478,192 +1503,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2965000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2911000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2758000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2735000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2764000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2741000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2607000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2551000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2832000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2793000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2626000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2650000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2886000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2547000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2711000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2441000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5710000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2731000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3451000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5276000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2582000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2804000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1640000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2584000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>494000</v>
+      </c>
+      <c r="E18" s="3">
         <v>915000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1511000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>443000</v>
       </c>
-      <c r="G18" s="3">
-        <v>554000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="I18" s="3">
         <v>677000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-533000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>622000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1060000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1174000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1494000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>812000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1639000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>601000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1078000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>634000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>80000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1459000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>762000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>332000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1453000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>428000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>710000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>839000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>405000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>103000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>600000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1696,175 +1728,179 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1254000</v>
+      </c>
+      <c r="E20" s="3">
         <v>615000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-917000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-841000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1422000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1309000</v>
+      </c>
+      <c r="I20" s="3">
         <v>199000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1858000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>159000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-535000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-185000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9400000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-453000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2057000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>548000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-524000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1726000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>750000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-174000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-445000</v>
-      </c>
       <c r="H21" s="3">
+        <v>456000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1089000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1361000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>923000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>686000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1077000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>390000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-709000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8241000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-962000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-242000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>22000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-629000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2493000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-748000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>566000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>638000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1877,287 +1913,299 @@
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>55000</v>
+        <v>57000</v>
       </c>
       <c r="E22" s="3">
         <v>55000</v>
       </c>
       <c r="F22" s="3">
+        <v>55000</v>
+      </c>
+      <c r="G22" s="3">
         <v>61000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>53000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>51000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>50000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>47000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>60000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>59000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>74000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>48000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>52000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>48000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>52000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>54000</v>
       </c>
       <c r="T22" s="3">
         <v>54000</v>
       </c>
       <c r="U22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="V22" s="3">
         <v>113000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>56000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>60000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>65000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>60000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>46000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>45000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>42000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>35000</v>
       </c>
       <c r="AE22" s="3">
         <v>35000</v>
       </c>
       <c r="AF22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-817000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1475000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>539000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-459000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-921000</v>
-      </c>
       <c r="H23" s="3">
+        <v>158000</v>
+      </c>
+      <c r="I23" s="3">
         <v>825000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1275000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>734000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>465000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>930000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>244000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-923000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6859000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-427000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-524000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-924000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2329000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-618000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>322000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>428000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>776000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>47000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>483000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-228000</v>
+      </c>
+      <c r="E24" s="3">
         <v>340000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-292000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-725000</v>
       </c>
-      <c r="G24" s="3">
-        <v>-208000</v>
-      </c>
       <c r="H24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I24" s="3">
         <v>177000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>264000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>137000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>77000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>165000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-408000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-885000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-218000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1075000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1434000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-259000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-121000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-213000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-215000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>448000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-259000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>50000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>63000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>225000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>30000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2248,192 +2296,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-589000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1135000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>831000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>266000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-713000</v>
-      </c>
       <c r="H26" s="3">
+        <v>138000</v>
+      </c>
+      <c r="I26" s="3">
         <v>648000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1011000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>597000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>388000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>765000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>223000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-705000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5425000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-850000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-306000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-311000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-709000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1881000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-359000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>272000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>365000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>551000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>106000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>524000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-724000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1050000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>733000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>163000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-815000</v>
-      </c>
       <c r="H27" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I27" s="3">
         <v>580000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>941000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>516000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>228000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>658000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>97000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-790000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5375000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-946000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-374000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-444000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-775000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1820000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-412000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>175000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>242000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>407000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>10000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>341000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2524,8 +2581,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2568,8 +2628,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2586,24 +2646,24 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>118000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>76000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2616,8 +2676,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2708,8 +2771,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2800,192 +2866,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1254000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-615000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>917000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>841000</v>
       </c>
-      <c r="G32" s="3">
-        <v>1422000</v>
-      </c>
       <c r="H32" s="3">
+        <v>1309000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-199000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-159000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>535000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>185000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1199000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2546000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3612000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1472000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6038000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1689000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>453000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1870000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1630000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2006000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>46000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>236000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>18000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>316000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>235000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-724000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1050000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>733000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>163000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-815000</v>
-      </c>
       <c r="H33" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I33" s="3">
         <v>580000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>941000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>516000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>228000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>658000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>97000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-790000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5375000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-946000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-374000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-444000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-775000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1938000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-496000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>164000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>214000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>483000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>10000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>341000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3076,197 +3151,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-724000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1050000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>733000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>163000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-815000</v>
-      </c>
       <c r="H35" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I35" s="3">
         <v>580000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>941000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>516000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>228000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>658000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>97000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-790000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5375000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-946000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-374000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-444000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-775000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1938000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-496000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>164000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>214000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>483000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>10000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>341000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3299,8 +3383,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3333,100 +3418,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8239000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6096000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7693000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5018000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4281000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4139000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5109000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5713000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5188000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5255000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5761000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6795000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6179000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8684000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8364000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10315000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4405000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4471000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4734000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5129000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4469000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4777000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6833000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3517,100 +3606,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10189000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10288000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10448000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10656000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10809000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15917000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16424000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16804000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17278000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17440000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16936000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6887000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6789000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6509000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6663000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7050000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6579000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6591000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6896000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6972000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7104000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7133000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7239000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3701,19 +3796,22 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>928000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>879000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1055000</v>
+        <v>868000</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -3754,29 +3852,29 @@
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U45" s="3">
         <v>958000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1110000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1262000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1170000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1263000</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
@@ -3793,8 +3891,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3885,100 +3986,106 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>104223000</v>
+      </c>
+      <c r="E47" s="3">
         <v>99244000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>99448000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>97517000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>93878000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>94739000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>94890000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>99887000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>105306000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>102300000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>100895000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>106006000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>109087000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>105778000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>102693000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>96216000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>93340000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>94690000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>86853000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>82880000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>81281000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>79209000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>76822000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4012,36 +4119,36 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P48" s="3">
         <v>691000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T48" s="3">
         <v>687000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>713000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>726000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>760000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4051,8 +4158,8 @@
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -4069,100 +4176,106 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5433000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5448000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5463000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5478000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5482000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5635000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4721000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4723000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4728000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4734000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4739000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4744000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4737000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4745000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4756000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4760000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4751000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4765000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4776000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4769000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4780000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4791000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4802000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4253,8 +4366,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4345,100 +4461,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7280000</v>
+        <v>7270000</v>
       </c>
       <c r="E52" s="3">
-        <v>7078000</v>
+        <v>8208000</v>
       </c>
       <c r="F52" s="3">
-        <v>7090000</v>
+        <v>7957000</v>
       </c>
       <c r="G52" s="3">
+        <v>8145000</v>
+      </c>
+      <c r="H52" s="3">
         <v>8453000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9579000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9288000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8285000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6995000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6275000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5911000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6839000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6466000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6040000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6064000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7665000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7894000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5787000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6080000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6018000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6745000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6736000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7635000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4529,100 +4651,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>276814000</v>
+      </c>
+      <c r="E54" s="3">
         <v>260252000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>269006000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>261500000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>252702000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>245600000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>253482000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>277658000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>292262000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>284579000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>285982000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>276832000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>275397000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>262496000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>254110000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>240781000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>249818000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>244646000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>238597000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>232819000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>220797000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>234451000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>231012000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4655,8 +4783,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4689,8 +4818,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4781,192 +4911,201 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8981000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9001000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8671000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9415000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9539000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7270000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6820000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5992000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6636000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7059000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8017000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9456000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5947000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5038000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4890000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4632000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4608000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4208000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1698000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1640000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2063000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2400000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2350000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5462000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4199000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5452000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4911000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6189000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5316000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5786000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7007000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6264000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5706000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5962000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6802000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7845000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7260000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7447000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8366000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6060000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6068000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6146000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6321000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5032000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4687000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4714000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5057,126 +5196,132 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10551000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11280000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12283000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12082000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11278000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4026000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5698000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5318000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11848000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4772000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4867000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5105000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7321000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5916000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5915000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6336000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6403000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7086000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7144000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7299000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7455000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7306000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7422000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E62" s="3">
         <v>216000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>129000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>158000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>108000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5185,26 +5330,26 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>270000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>322000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>679000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>724000</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5217,8 +5362,8 @@
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -5241,8 +5386,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5333,8 +5481,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5425,8 +5576,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5517,100 +5671,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>274165000</v>
+      </c>
+      <c r="E66" s="3">
         <v>258610000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>265453000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>257746000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>251301000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>242246000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>247893000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>269704000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>280743000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>272899000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>274250000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>266139000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>259821000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>245196000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>236516000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>220695000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>236362000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>229710000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>223754000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>219676000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>206931000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>222040000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>217674000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5643,8 +5803,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5735,8 +5896,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5827,8 +5991,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5866,13 +6033,13 @@
         <v>1562000</v>
       </c>
       <c r="O70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="P70" s="3">
         <v>1269000</v>
       </c>
       <c r="Q70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="R70" s="3">
         <v>775000</v>
@@ -5881,7 +6048,7 @@
         <v>775000</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -5919,8 +6086,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6011,100 +6181,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10243000</v>
+      </c>
+      <c r="E72" s="3">
         <v>11163000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10325000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9806000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9825000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10839000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10718000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9312000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8880000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8857000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8739000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8758000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10699000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12032000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12995000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17112000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11744000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12835000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13293000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13004000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13989000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12031000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12613000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6195,8 +6371,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6287,8 +6466,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6379,100 +6561,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1087000</v>
+      </c>
+      <c r="E76" s="3">
         <v>80000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1991000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2192000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-161000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1792000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4027000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6392000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9957000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10118000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10170000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9131000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14307000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16031000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16819000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19311000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12681000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14936000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14843000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13143000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13866000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12411000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13338000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6563,197 +6751,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-724000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1050000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>733000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>163000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-815000</v>
-      </c>
       <c r="H81" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I81" s="3">
         <v>580000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>941000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>516000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>228000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>658000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>97000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-790000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5375000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-946000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-374000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-444000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-775000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1938000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-496000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>164000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>214000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>483000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>10000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>341000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6786,100 +6983,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E83" s="3">
         <v>196000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>156000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>224000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>227000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>216000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>191000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>180000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>161000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>88000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>95000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>153000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>89000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>162000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>176000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1330000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>93000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>131000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>433000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>239000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>104000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>-195000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>184000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>164000</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>8</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6970,8 +7171,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7062,8 +7266,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7154,8 +7361,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7246,8 +7456,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7338,100 +7551,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-392000</v>
+      </c>
+      <c r="E89" s="3">
         <v>410000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>361000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-587000</v>
       </c>
-      <c r="G89" s="3">
-        <v>-540000</v>
-      </c>
       <c r="H89" s="3">
+        <v>61000</v>
+      </c>
+      <c r="I89" s="3">
         <v>229000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>68000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-608000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-402000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>241000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-581000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-66000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>553000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-570000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>76000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>133000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-425000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-109000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>94000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>281000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-67000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>378000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>666000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>72000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7464,100 +7683,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-39000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-65000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-83000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-29000</v>
       </c>
       <c r="M91" s="3">
         <v>-29000</v>
       </c>
       <c r="N91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-23000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-63000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-14000</v>
       </c>
       <c r="R91" s="3">
         <v>-14000</v>
       </c>
       <c r="S91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-21000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-33000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-39000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-39000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-38000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7648,8 +7871,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7740,100 +7966,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-171000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>4147000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-70000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-993000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1348000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>459000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7866,83 +8098,84 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-77000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-78000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-72000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-75000</v>
       </c>
       <c r="I96" s="3">
         <v>-75000</v>
       </c>
       <c r="J96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-70000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-72000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-74000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-76000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-74000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-75000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-77000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-69000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-70000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-74000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-141000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-68000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-69000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-73000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -7958,8 +8191,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8050,8 +8286,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8142,8 +8381,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8234,280 +8476,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2387000</v>
+      </c>
+      <c r="E100" s="3">
         <v>470000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3394000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2749000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3588000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1513000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1108000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1437000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2330000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1751000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3994000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4436000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1498000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5285000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>557000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2334000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>992000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4581000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3132000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>838000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-181000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>700000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-264000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>954000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>34000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-38000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-41000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>12000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-13000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>16000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-8000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>1000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-3000</v>
       </c>
       <c r="X101" s="3">
         <v>-3000</v>
       </c>
       <c r="Y101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>11000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2135000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2674000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>742000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>301000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-970000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-604000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>525000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-506000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>669000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>320000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5886000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-263000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>265000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>660000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-308000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>742000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>259000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>533000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-593000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,409 +656,421 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4706000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3459000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3826000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4269000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3178000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4261000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3284000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2018000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3454000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3853000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3800000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4144000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3698000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4186000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3312000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3519000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3221000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3365000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3531000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6735000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3344000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3136000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3093000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3012000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1651000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1703000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1571000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1577000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1500000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1395000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1305000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1559000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1461000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1492000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1534000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1612000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1441000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1682000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1345000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3431000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1490000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2372000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3028000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1465000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1376000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1021000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1455000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>876000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3025000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1808000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2123000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2698000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1601000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2761000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1889000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>713000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1895000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2392000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2308000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2610000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2086000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2745000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1630000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2174000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-210000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1875000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1159000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3707000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1879000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1760000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2072000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1557000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1092,8 +1104,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1187,8 +1200,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1318,67 +1337,70 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-5000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>58000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>31000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>38000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>7000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>25800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>27200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>35000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>24300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1472,8 +1494,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1504,198 +1529,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3026000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2965000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2911000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2758000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2735000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2741000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2607000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2551000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2832000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2793000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2626000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2650000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2886000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2547000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2711000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2441000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5710000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2731000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3451000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5276000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2582000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2804000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1640000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2584000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1680000</v>
+      </c>
+      <c r="E18" s="3">
         <v>494000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>915000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1511000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>443000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1520000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>677000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-533000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>622000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1060000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1174000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1494000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>812000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1639000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>601000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1078000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>634000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>80000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1459000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>762000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>332000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1453000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>428000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>710000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>839000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>405000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>103000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>600000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1729,181 +1761,185 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1376000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1254000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>615000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-917000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-841000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>199000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1858000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>159000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-535000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-185000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9400000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-453000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2057000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>548000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>544000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-524000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1726000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>750000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-174000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>456000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1089000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1361000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>923000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>686000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1077000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>390000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-709000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8241000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-962000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-242000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-629000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2493000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-748000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>566000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>638000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1916,11 +1952,14 @@
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1928,284 +1967,293 @@
         <v>57000</v>
       </c>
       <c r="E22" s="3">
-        <v>55000</v>
+        <v>57000</v>
       </c>
       <c r="F22" s="3">
         <v>55000</v>
       </c>
       <c r="G22" s="3">
+        <v>55000</v>
+      </c>
+      <c r="H22" s="3">
         <v>61000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>53000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>51000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>50000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>47000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>60000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>59000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>51000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>74000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>48000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>52000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>48000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>52000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>54000</v>
       </c>
       <c r="U22" s="3">
         <v>54000</v>
       </c>
       <c r="V22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="W22" s="3">
         <v>113000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>56000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>60000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>65000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>60000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>46000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>45000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>42000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>35000</v>
       </c>
       <c r="AF22" s="3">
         <v>35000</v>
       </c>
       <c r="AG22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-817000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1475000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>539000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-459000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>158000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>825000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1275000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>734000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>465000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>930000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>244000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-923000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6859000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-427000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-524000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-924000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2329000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-618000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>322000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>428000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>776000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>47000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>483000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-228000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>340000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-292000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-725000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>20000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>177000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>264000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>137000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>77000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>165000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>21000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-408000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-885000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-218000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1075000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1434000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-259000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-121000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-213000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-215000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>448000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-259000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>50000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>63000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>225000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>30000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2299,198 +2347,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-589000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1135000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>831000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>266000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>138000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>648000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1011000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>597000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>388000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>765000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>223000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-705000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5425000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-850000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-306000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-311000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-709000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1881000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-359000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>272000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>365000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>551000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>106000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>524000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-724000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1050000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>733000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>163000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>580000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>941000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>516000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>228000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>658000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>97000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-790000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5375000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-946000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-374000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-444000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-775000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1820000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-412000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>175000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>242000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>407000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>341000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2584,8 +2641,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2631,8 +2691,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2649,24 +2709,24 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>118000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>76000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2679,8 +2739,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2774,8 +2837,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2869,198 +2935,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1376000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1254000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-615000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>917000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>841000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1309000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-199000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-159000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>535000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>185000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1199000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2546000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3612000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1472000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6038000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1689000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>453000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1870000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1630000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2006000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>46000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>236000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>18000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>316000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>235000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-724000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1050000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>733000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>163000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>36000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>580000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>941000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>516000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>228000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>658000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>97000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-790000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5375000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-946000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-374000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-444000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-775000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1938000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-496000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>164000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>214000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>483000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>341000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3154,203 +3229,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-724000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1050000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>733000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>163000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>36000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>580000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>941000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>516000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>228000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>658000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>97000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-790000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5375000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-946000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-374000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-444000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-775000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1938000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-496000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>164000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>214000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>483000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>341000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3384,8 +3468,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3419,103 +3504,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10357000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8239000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6096000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7693000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5018000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4281000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4139000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5109000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5713000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5188000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5255000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5761000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6795000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6179000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8684000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8364000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10315000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4405000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4471000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4734000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5129000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4469000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4777000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3609,103 +3698,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10195000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10189000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10288000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10448000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10656000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10809000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15917000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16424000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16804000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17278000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17440000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16936000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6887000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6789000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6509000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6663000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7050000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6579000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6591000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6896000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6972000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7104000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7133000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7239000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3799,17 +3894,20 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E45" s="3">
         <v>868000</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3855,29 +3953,29 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V45" s="3">
         <v>958000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1110000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1262000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1170000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1263000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -3894,8 +3992,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3989,103 +4090,109 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>104683000</v>
+      </c>
+      <c r="E47" s="3">
         <v>104223000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>99244000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>99448000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>97517000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>93878000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>94739000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>94890000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>99887000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>105306000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>102300000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>100895000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>106006000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>109087000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>105778000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>102693000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>96216000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>93340000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>94690000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>86853000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>82880000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>81281000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>79209000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>76822000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4122,36 +4229,36 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48" s="3">
         <v>691000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U48" s="3">
         <v>687000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>713000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>726000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>760000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4161,8 +4268,8 @@
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -4179,103 +4286,109 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5419000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5433000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5448000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5463000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5478000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5482000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5635000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4721000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4723000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4728000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4734000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4739000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4744000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4737000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4745000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4756000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4760000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4751000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4765000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4776000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4769000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4780000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4791000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4802000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4369,8 +4482,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4464,103 +4580,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7549000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7270000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8208000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7957000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8145000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8453000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9579000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9288000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8285000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6995000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6275000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5911000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6839000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6466000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6040000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6064000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7665000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7894000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5787000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6080000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6018000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6745000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6736000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7635000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4654,103 +4776,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>285577000</v>
+      </c>
+      <c r="E54" s="3">
         <v>276814000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>260252000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>269006000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>261500000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>252702000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>245600000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>253482000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>277658000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>292262000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>284579000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>285982000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>276832000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>275397000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>262496000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>254110000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>240781000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>249818000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>244646000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>238597000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>232819000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>220797000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>234451000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>231012000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4784,8 +4912,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4819,8 +4948,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4914,198 +5044,207 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8298000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8981000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9001000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8671000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9415000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9539000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7270000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6820000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5992000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6636000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7059000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8017000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9456000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5947000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5038000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4890000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4632000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4608000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4208000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1698000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1640000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2063000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2400000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2350000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4561000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5462000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4199000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5452000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4911000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6189000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5316000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5786000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7007000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6264000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5706000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5962000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6802000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7845000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7260000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7447000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8366000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6060000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6068000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6146000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6321000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5032000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4687000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4714000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5199,132 +5338,138 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10536000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10551000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11280000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12283000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12082000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11278000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4026000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5698000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5318000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11848000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4772000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4867000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5105000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7321000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5916000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5915000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6336000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6403000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7086000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7144000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7299000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7455000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7306000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7422000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>239000</v>
+      </c>
+      <c r="E62" s="3">
         <v>153000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>216000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>129000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>158000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>108000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5333,26 +5478,26 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>270000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>322000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>679000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>724000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5365,8 +5510,8 @@
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -5389,8 +5534,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5484,8 +5632,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5579,8 +5730,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5674,103 +5828,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>283545000</v>
+      </c>
+      <c r="E66" s="3">
         <v>274165000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>258610000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>265453000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>257746000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>251301000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>242246000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>247893000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>269704000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>280743000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>272899000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>274250000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>266139000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>259821000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>245196000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>236516000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>220695000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>236362000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>229710000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>223754000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>219676000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>206931000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>222040000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>217674000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5804,8 +5964,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5899,8 +6060,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5994,8 +6158,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6036,13 +6203,13 @@
         <v>1562000</v>
       </c>
       <c r="P70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="Q70" s="3">
         <v>1269000</v>
       </c>
       <c r="R70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="S70" s="3">
         <v>775000</v>
@@ -6051,7 +6218,7 @@
         <v>775000</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -6089,8 +6256,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6184,103 +6354,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10110000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10243000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11163000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10325000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9806000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9825000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10839000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10718000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9312000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8880000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8857000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8739000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8758000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10699000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12032000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12995000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17112000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11744000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12835000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13293000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13004000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13989000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12031000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12613000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6374,8 +6550,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6469,8 +6648,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6564,103 +6746,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1087000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>80000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1991000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2192000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-161000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1792000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4027000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6392000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9957000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10118000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10170000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9131000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14307000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16031000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16819000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19311000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12681000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14936000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14843000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13143000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13866000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12411000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13338000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6754,203 +6942,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-724000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1050000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>733000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>163000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>36000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>580000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>941000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>516000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>228000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>658000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>97000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-790000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5375000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-946000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-374000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-444000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-775000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1938000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-496000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>164000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>214000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>483000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>341000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6984,103 +7181,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E83" s="3">
         <v>236000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>196000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>156000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>224000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>227000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>216000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>191000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>180000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>161000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>88000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>95000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>153000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>89000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>162000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>176000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1330000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>93000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>131000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>433000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>239000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>104000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>-195000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>184000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>164000</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
-      </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>8</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7174,8 +7375,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7269,8 +7473,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7364,8 +7571,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7459,8 +7669,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7554,103 +7767,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-392000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>410000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>361000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-587000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>61000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>229000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>68000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-608000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-402000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>241000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-581000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-66000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>553000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-570000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>76000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>133000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-425000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-109000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>94000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>281000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-67000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>378000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>666000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>72000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7684,103 +7903,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-39000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-65000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-83000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-29000</v>
       </c>
       <c r="N91" s="3">
         <v>-29000</v>
       </c>
       <c r="O91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-23000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-14000</v>
       </c>
       <c r="S91" s="3">
         <v>-14000</v>
       </c>
       <c r="T91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-21000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-33000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-39000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-16000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-39000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-38000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7874,8 +8097,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7969,103 +8195,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2682000</v>
+      </c>
+      <c r="E94" s="3">
         <v>115000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-171000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4147000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-70000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-993000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1348000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>459000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8099,86 +8331,87 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-74000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-77000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-78000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-72000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-75000</v>
       </c>
       <c r="J96" s="3">
         <v>-75000</v>
       </c>
       <c r="K96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-70000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-72000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-74000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-76000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-74000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-75000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-76000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-77000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-69000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-70000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-74000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-141000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-68000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-69000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-73000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -8194,8 +8427,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8289,8 +8525,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8384,8 +8623,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8479,289 +8721,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4945000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2387000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>470000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3394000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2749000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3588000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1513000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1108000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1437000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2330000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1751000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3994000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4436000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1498000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5285000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>557000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2334000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>992000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4581000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3132000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>838000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-181000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>700000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-264000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>954000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E101" s="3">
         <v>25000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>10000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>34000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-38000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-41000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>22000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>12000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-13000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>16000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-8000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>1000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-3000</v>
       </c>
       <c r="Y101" s="3">
         <v>-3000</v>
       </c>
       <c r="Z101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>11000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2284000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2135000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2674000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>742000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>301000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-970000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-604000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>525000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-506000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>669000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>320000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5886000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-263000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>265000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>660000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-308000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>742000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>259000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>533000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-593000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,421 +656,433 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3851000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4706000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3459000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3826000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4269000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3178000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4261000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3284000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2018000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3454000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3853000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3800000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4144000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3698000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4186000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3312000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3519000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3221000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3365000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3531000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6735000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3344000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3136000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3093000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3012000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1727000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1681000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1651000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1703000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1571000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1577000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1500000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1395000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1305000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1559000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1461000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1492000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1534000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1612000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1441000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1682000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1345000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3431000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1490000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2372000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3028000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1465000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1376000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1021000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1455000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>876000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2124000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3025000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1808000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2123000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2698000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1601000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2761000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1889000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>713000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1895000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2392000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2308000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2610000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2086000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2745000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1630000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2174000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-210000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1875000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1159000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3707000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1879000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1760000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1557000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1105,8 +1117,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1203,8 +1216,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1317,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1340,67 +1359,70 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-5000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>58000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>31000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>38000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>7000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>25800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>27200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>35000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>24300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1497,8 +1519,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1530,204 +1555,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2900000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3026000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2965000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2911000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2758000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2735000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2741000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2607000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2551000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2832000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2793000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2626000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2650000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2886000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2547000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2711000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2441000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5710000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2731000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3451000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5276000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2582000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2804000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1640000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2584000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>951000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1680000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>494000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>915000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1511000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>443000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1520000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>677000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-533000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>622000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1060000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1174000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1494000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>812000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1639000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>601000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1078000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>634000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>80000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1459000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>762000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>332000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1453000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>428000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>710000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>839000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>405000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>103000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>600000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1762,187 +1794,191 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-208000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1376000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1254000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>615000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-917000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-841000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>199000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1858000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>159000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-535000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-185000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>9400000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-453000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2057000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>548000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>932000</v>
+      </c>
+      <c r="E21" s="3">
         <v>544000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-524000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1726000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>750000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-174000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>456000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1089000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1361000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>923000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>686000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1077000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>390000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-709000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8241000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-962000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-242000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-629000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2493000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-748000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>566000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>638000</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1955,305 +1991,317 @@
       <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>57000</v>
+        <v>62000</v>
       </c>
       <c r="E22" s="3">
         <v>57000</v>
       </c>
       <c r="F22" s="3">
-        <v>55000</v>
+        <v>57000</v>
       </c>
       <c r="G22" s="3">
         <v>55000</v>
       </c>
       <c r="H22" s="3">
+        <v>55000</v>
+      </c>
+      <c r="I22" s="3">
         <v>61000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>53000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>51000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>50000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>47000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>60000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>59000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>51000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>74000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>48000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>52000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>48000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>52000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>54000</v>
       </c>
       <c r="V22" s="3">
         <v>54000</v>
       </c>
       <c r="W22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="X22" s="3">
         <v>113000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>56000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>60000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>65000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>60000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>46000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>45000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>42000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>35000</v>
       </c>
       <c r="AG22" s="3">
         <v>35000</v>
       </c>
       <c r="AH22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>681000</v>
+      </c>
+      <c r="E23" s="3">
         <v>247000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-817000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1475000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>539000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-459000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>158000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>825000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1275000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>734000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>465000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>930000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>244000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-923000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6859000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-427000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-524000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-924000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2329000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-618000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>322000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>428000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>776000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>47000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>483000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E24" s="3">
         <v>30000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-228000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>340000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-292000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-725000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>20000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>177000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>264000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>137000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>77000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>165000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-408000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-885000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-218000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1075000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1434000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-259000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-121000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-213000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-215000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>448000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-259000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>50000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>63000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>225000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>30000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2350,204 +2398,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>565000</v>
+      </c>
+      <c r="E26" s="3">
         <v>217000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-589000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1135000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>831000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>266000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>138000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>648000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1011000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>597000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>388000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>765000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>223000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-705000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5425000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-850000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-306000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-311000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-709000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1881000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-359000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>272000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>365000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>551000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>106000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>524000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>402000</v>
+      </c>
+      <c r="E27" s="3">
         <v>100000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-724000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1050000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>733000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>163000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>36000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>580000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>941000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>516000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>228000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>658000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>97000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-790000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5375000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-946000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-374000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-444000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-775000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1820000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>175000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>242000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>407000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>10000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>341000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2644,8 +2701,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2694,8 +2754,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2712,24 +2772,24 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>118000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>76000</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2742,8 +2802,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2840,8 +2903,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2938,204 +3004,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1376000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1254000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-615000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>917000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>841000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1309000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-199000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-159000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>535000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>185000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1199000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2546000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3612000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1472000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6038000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1689000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>453000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1870000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1630000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2006000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>46000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>236000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>18000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>316000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>235000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>402000</v>
+      </c>
+      <c r="E33" s="3">
         <v>100000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-724000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1050000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>733000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>163000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>36000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>580000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>941000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>516000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>228000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>658000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>97000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-790000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5375000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-946000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-374000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-444000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-775000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1938000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-496000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>164000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>214000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>483000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>341000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3232,209 +3307,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>402000</v>
+      </c>
+      <c r="E35" s="3">
         <v>100000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-724000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1050000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>733000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>163000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>36000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>580000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>941000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>516000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>228000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>658000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>97000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-790000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5375000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-946000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-374000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-444000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-775000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1938000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-496000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>164000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>214000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>483000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>341000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3469,8 +3553,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3505,106 +3590,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9684000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10357000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8239000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6096000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7693000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5018000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4281000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4139000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5109000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5713000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5188000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5255000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5761000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6795000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6179000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8684000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8364000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10315000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4405000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4471000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4734000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5129000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4469000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4777000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3701,106 +3790,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10038000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10195000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10189000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10288000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10448000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10656000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10809000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15917000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16424000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16804000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17278000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>17440000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16936000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6887000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6789000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6509000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6663000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7050000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6579000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6591000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6896000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6972000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7104000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7133000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7239000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3897,20 +3992,23 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>592000</v>
+      </c>
+      <c r="E45" s="3">
         <v>866000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>868000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3956,29 +4054,29 @@
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>958000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1110000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1262000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1170000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1263000</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -3995,8 +4093,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4093,106 +4194,112 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>109843000</v>
+      </c>
+      <c r="E47" s="3">
         <v>104683000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>104223000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>99244000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>99448000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>97517000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>93878000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>94739000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>94890000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>99887000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>105306000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>102300000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>100895000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>106006000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>109087000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>105778000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>102693000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>96216000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>93340000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>94690000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>86853000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>82880000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>81281000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>79209000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>76822000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4232,36 +4339,36 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="3">
         <v>691000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V48" s="3">
         <v>687000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>713000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>726000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>760000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4271,8 +4378,8 @@
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -4289,106 +4396,112 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5403000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5419000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5433000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5448000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5463000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5478000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5482000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5635000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4721000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4723000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4728000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4734000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4739000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4744000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4737000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4745000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4756000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4760000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4751000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4765000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4776000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4769000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4780000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4791000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4802000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4485,8 +4598,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4583,106 +4699,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6924000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7549000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7270000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8208000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7957000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8145000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8453000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9579000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9288000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8285000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6995000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6275000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5911000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6839000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6466000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6040000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6064000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7665000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7894000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5787000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6080000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6018000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6745000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6736000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7635000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4779,106 +4901,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>287769000</v>
+      </c>
+      <c r="E54" s="3">
         <v>285577000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>276814000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>260252000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>269006000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>261500000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>252702000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>245600000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>253482000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>277658000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>292262000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>284579000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>285982000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>276832000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>275397000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>262496000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>254110000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>240781000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>249818000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>244646000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>238597000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>232819000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>220797000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>234451000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>231012000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4913,8 +5041,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4949,8 +5078,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5047,204 +5177,213 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8583000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8298000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8981000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9001000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8671000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9415000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9539000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7270000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6820000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5992000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6636000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7059000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8017000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9456000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5947000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5038000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4890000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4632000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4608000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4208000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1698000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1640000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2063000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2400000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2350000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4262000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4561000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5462000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4199000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5452000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4911000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6189000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5316000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5786000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7007000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6264000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5706000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5962000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6802000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7845000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7260000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7447000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8366000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6060000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6068000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6146000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6321000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5032000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4687000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4714000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5341,138 +5480,144 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10417000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10536000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10551000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11280000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12283000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12082000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11278000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4026000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5698000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5318000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11848000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4772000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4867000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5105000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7321000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5916000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5915000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6336000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6403000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7086000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7144000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7299000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7455000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7306000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7422000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>239000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>153000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>216000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>129000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>158000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>108000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5481,26 +5626,26 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>270000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>322000</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
       <c r="S62" s="3">
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>679000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>724000</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5513,8 +5658,8 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5537,8 +5682,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5635,8 +5783,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5733,8 +5884,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5831,106 +5985,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>286125000</v>
+      </c>
+      <c r="E66" s="3">
         <v>283545000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>274165000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>258610000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>265453000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>257746000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>251301000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>242246000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>247893000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>269704000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>280743000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>272899000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>274250000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>266139000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>259821000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>245196000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>236516000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>220695000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>236362000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>229710000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>223754000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>219676000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>206931000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>222040000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>217674000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5965,8 +6125,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6063,8 +6224,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6161,8 +6325,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6206,13 +6373,13 @@
         <v>1562000</v>
       </c>
       <c r="Q70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="R70" s="3">
         <v>1269000</v>
       </c>
       <c r="S70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="T70" s="3">
         <v>775000</v>
@@ -6221,7 +6388,7 @@
         <v>775000</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -6259,8 +6426,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6357,106 +6527,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10317000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10110000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10243000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11163000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10325000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9806000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9825000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10839000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10718000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9312000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8880000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8857000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8739000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8758000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10699000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12032000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12995000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17112000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11744000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12835000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13293000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13004000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13989000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12031000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12613000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6553,8 +6729,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6651,8 +6830,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6749,106 +6931,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E76" s="3">
         <v>470000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1087000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>80000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1991000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2192000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-161000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1792000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4027000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6392000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9957000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10118000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10170000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9131000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14307000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16031000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16819000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19311000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12681000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14936000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14843000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13143000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13866000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12411000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13338000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6945,209 +7133,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>402000</v>
+      </c>
+      <c r="E81" s="3">
         <v>100000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-724000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1050000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>733000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>163000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>36000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>580000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>941000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>516000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>228000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>658000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>97000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-790000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5375000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-946000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-374000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-444000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-775000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1938000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-496000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>164000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>214000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>483000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>341000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7182,106 +7379,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E83" s="3">
         <v>240000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>236000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>196000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>156000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>224000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>227000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>216000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>191000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>180000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>161000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>88000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>95000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>153000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>89000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>162000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>176000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1330000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>93000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>131000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>433000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>239000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>104000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>-195000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>184000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>164000</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>8</v>
+      <c r="AF83" s="3">
+        <v>0</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7378,8 +7579,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7476,8 +7680,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7574,8 +7781,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7672,8 +7882,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7770,106 +7983,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>892000</v>
+      </c>
+      <c r="E89" s="3">
         <v>31000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-392000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>410000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>361000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-587000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>61000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>229000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>68000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-608000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-402000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>241000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-581000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-66000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>553000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-570000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>76000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>133000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-425000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-109000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>94000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>281000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-67000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>378000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>666000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>72000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7904,106 +8123,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-63000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-35000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-39000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-65000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-83000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-29000</v>
       </c>
       <c r="O91" s="3">
         <v>-29000</v>
       </c>
       <c r="P91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-63000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-14000</v>
       </c>
       <c r="T91" s="3">
         <v>-14000</v>
       </c>
       <c r="U91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-21000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-33000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-39000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-39000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8100,8 +8323,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8198,106 +8424,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5245000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2682000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>115000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-171000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>4147000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-993000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1348000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>459000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8332,89 +8564,90 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-73000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-74000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-77000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-78000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-72000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-75000</v>
       </c>
       <c r="K96" s="3">
         <v>-75000</v>
       </c>
       <c r="L96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-70000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-72000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-74000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-76000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-75000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-76000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-77000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-69000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-70000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-74000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-141000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-68000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-69000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -8430,8 +8663,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8528,8 +8764,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8626,8 +8865,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8724,298 +8966,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3364000</v>
+      </c>
+      <c r="E100" s="3">
         <v>4945000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2387000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>470000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3394000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2749000</v>
       </c>
-      <c r="I100" s="3">
-        <v>3588000</v>
-      </c>
       <c r="J100" s="3">
+        <v>3589000</v>
+      </c>
+      <c r="K100" s="3">
         <v>1513000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1108000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1437000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2330000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1751000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3994000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4436000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1498000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5285000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>557000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2334000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>992000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4581000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3132000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>838000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-181000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>700000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-264000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>954000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>25000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-18000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>34000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-38000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-41000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>22000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>12000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-13000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>16000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8000</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-3000</v>
       </c>
       <c r="Z101" s="3">
         <v>-3000</v>
       </c>
       <c r="AA101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>8000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>11000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-992000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2284000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2135000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2674000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>742000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>301000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-970000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-604000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>525000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-506000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>669000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>320000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5886000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-263000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>265000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>660000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-308000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>742000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>259000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>533000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-593000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,433 +656,445 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3851000</v>
+        <v>2933000</v>
       </c>
       <c r="E8" s="3">
-        <v>4706000</v>
+        <v>3763000</v>
       </c>
       <c r="F8" s="3">
-        <v>3459000</v>
+        <v>2230000</v>
       </c>
       <c r="G8" s="3">
-        <v>3826000</v>
+        <v>1861000</v>
       </c>
       <c r="H8" s="3">
-        <v>4269000</v>
+        <v>3912000</v>
       </c>
       <c r="I8" s="3">
-        <v>3178000</v>
+        <v>2386000</v>
       </c>
       <c r="J8" s="3">
+        <v>2357000</v>
+      </c>
+      <c r="K8" s="3">
         <v>4261000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3284000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2018000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3454000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3853000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3800000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4144000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3698000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4186000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3312000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3519000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3221000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3365000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3531000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6735000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3344000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3136000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3093000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3012000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1727000</v>
+        <v>1056000</v>
       </c>
       <c r="E9" s="3">
-        <v>1681000</v>
+        <v>1040000</v>
       </c>
       <c r="F9" s="3">
-        <v>1651000</v>
+        <v>1057000</v>
       </c>
       <c r="G9" s="3">
-        <v>1703000</v>
+        <v>998000</v>
       </c>
       <c r="H9" s="3">
-        <v>1571000</v>
+        <v>998000</v>
       </c>
       <c r="I9" s="3">
-        <v>1577000</v>
+        <v>959000</v>
       </c>
       <c r="J9" s="3">
+        <v>963000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1500000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1395000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1305000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1559000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1461000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1492000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1534000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1612000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1441000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1682000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1345000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3431000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1490000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2372000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3028000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1465000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1376000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1021000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1455000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>876000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2124000</v>
+        <v>227000</v>
       </c>
       <c r="E10" s="3">
-        <v>3025000</v>
+        <v>1423000</v>
       </c>
       <c r="F10" s="3">
-        <v>1808000</v>
+        <v>857000</v>
       </c>
       <c r="G10" s="3">
-        <v>2123000</v>
+        <v>-510000</v>
       </c>
       <c r="H10" s="3">
-        <v>2698000</v>
+        <v>2268000</v>
       </c>
       <c r="I10" s="3">
-        <v>1601000</v>
+        <v>1069000</v>
       </c>
       <c r="J10" s="3">
+        <v>25000</v>
+      </c>
+      <c r="K10" s="3">
         <v>2761000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1889000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>713000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1895000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2392000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2308000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2610000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2086000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2745000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1630000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2174000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-210000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1875000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1159000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3707000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1879000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1760000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1557000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1118,8 +1130,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1219,8 +1232,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,31 +1336,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1362,90 +1381,93 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>58000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>31000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>38000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>7000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>25800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>27200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>35000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>24300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>211000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>183000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>196000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>156000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>224000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1522,8 +1544,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1556,210 +1581,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2900000</v>
+        <v>3035000</v>
       </c>
       <c r="E17" s="3">
-        <v>3026000</v>
+        <v>2767000</v>
       </c>
       <c r="F17" s="3">
-        <v>2965000</v>
+        <v>1926000</v>
       </c>
       <c r="G17" s="3">
-        <v>2911000</v>
+        <v>2930000</v>
       </c>
       <c r="H17" s="3">
-        <v>2758000</v>
+        <v>2094000</v>
       </c>
       <c r="I17" s="3">
-        <v>2735000</v>
+        <v>1783000</v>
       </c>
       <c r="J17" s="3">
+        <v>2755000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2741000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2607000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2551000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2832000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2793000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2626000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2650000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2886000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2547000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2711000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2441000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5710000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2731000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3451000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5276000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2582000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2804000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1640000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2584000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>951000</v>
+        <v>-102000</v>
       </c>
       <c r="E18" s="3">
-        <v>1680000</v>
+        <v>996000</v>
       </c>
       <c r="F18" s="3">
-        <v>494000</v>
+        <v>304000</v>
       </c>
       <c r="G18" s="3">
-        <v>915000</v>
+        <v>-1069000</v>
       </c>
       <c r="H18" s="3">
-        <v>1511000</v>
+        <v>1818000</v>
       </c>
       <c r="I18" s="3">
-        <v>443000</v>
+        <v>603000</v>
       </c>
       <c r="J18" s="3">
+        <v>-398000</v>
+      </c>
+      <c r="K18" s="3">
         <v>1520000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>677000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-533000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>622000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1060000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1174000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1494000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>812000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1639000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>601000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1078000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>634000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>80000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1459000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>762000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>332000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1453000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>428000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>710000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>839000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>405000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>103000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>600000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1795,193 +1827,197 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-208000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1376000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1254000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>615000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-917000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-841000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>199000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1858000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>159000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-535000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-185000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9400000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-453000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2057000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>548000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>932000</v>
+        <v>109000</v>
       </c>
       <c r="E21" s="3">
+        <v>1185000</v>
+      </c>
+      <c r="F21" s="3">
         <v>544000</v>
       </c>
-      <c r="F21" s="3">
-        <v>-524000</v>
-      </c>
       <c r="G21" s="3">
-        <v>1726000</v>
+        <v>-886000</v>
       </c>
       <c r="H21" s="3">
-        <v>750000</v>
+        <v>2014000</v>
       </c>
       <c r="I21" s="3">
+        <v>759000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-174000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>456000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1089000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1361000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>923000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>686000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1077000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>390000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-709000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8241000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-962000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-242000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-629000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2493000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-748000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>566000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>638000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1994,314 +2030,326 @@
       <c r="AH21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>62000</v>
+        <v>-88000</v>
       </c>
       <c r="E22" s="3">
-        <v>57000</v>
+        <v>315000</v>
       </c>
       <c r="F22" s="3">
         <v>57000</v>
       </c>
       <c r="G22" s="3">
-        <v>55000</v>
+        <v>-252000</v>
       </c>
       <c r="H22" s="3">
-        <v>55000</v>
+        <v>343000</v>
       </c>
       <c r="I22" s="3">
+        <v>64000</v>
+      </c>
+      <c r="J22" s="3">
         <v>61000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>53000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>51000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>50000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>60000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>59000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>51000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>74000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>48000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>52000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>48000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>52000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>54000</v>
       </c>
       <c r="W22" s="3">
         <v>54000</v>
       </c>
       <c r="X22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>113000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>56000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>60000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>65000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>60000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>46000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>45000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>42000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>35000</v>
       </c>
       <c r="AH22" s="3">
         <v>35000</v>
       </c>
       <c r="AI22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E23" s="3">
         <v>681000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>247000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-817000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1475000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>539000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-459000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>158000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>825000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1275000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>734000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>465000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>930000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>244000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-923000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6859000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-427000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-524000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-924000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2329000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-618000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>322000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>428000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>776000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>47000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>483000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E24" s="3">
         <v>116000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-228000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>340000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-292000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-725000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>177000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>264000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>137000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>77000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>165000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>21000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-408000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-885000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-218000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1075000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1434000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-259000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-121000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-213000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-215000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>448000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-259000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>50000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>63000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>225000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>30000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2401,210 +2449,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E26" s="3">
         <v>565000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>217000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-589000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1135000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>831000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>266000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>138000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>648000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1011000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>597000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>388000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>765000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>223000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-705000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5425000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-850000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-306000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-311000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-709000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1881000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-359000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>272000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>365000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>551000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>106000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>524000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E27" s="3">
         <v>402000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>100000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-724000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1050000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>733000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>163000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>36000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>580000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>941000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>516000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>228000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>658000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>97000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-790000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5375000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-946000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-374000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-444000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-775000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1820000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>175000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>242000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>407000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>10000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>341000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2704,8 +2761,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2757,8 +2817,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2775,24 +2835,24 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>118000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>76000</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2805,8 +2865,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2906,8 +2969,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3007,210 +3073,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>208000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1376000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1254000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-615000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>917000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>841000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>1309000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-199000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-159000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>535000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>185000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1199000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2546000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3612000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1472000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6038000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1689000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>453000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1870000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1630000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2006000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>46000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>236000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>18000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>316000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>235000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>402000</v>
+        <v>-134000</v>
       </c>
       <c r="E33" s="3">
-        <v>100000</v>
+        <v>428000</v>
       </c>
       <c r="F33" s="3">
-        <v>-724000</v>
+        <v>114000</v>
       </c>
       <c r="G33" s="3">
-        <v>1050000</v>
+        <v>-698000</v>
       </c>
       <c r="H33" s="3">
-        <v>733000</v>
+        <v>1064000</v>
       </c>
       <c r="I33" s="3">
-        <v>163000</v>
+        <v>759000</v>
       </c>
       <c r="J33" s="3">
+        <v>177000</v>
+      </c>
+      <c r="K33" s="3">
         <v>36000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>580000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>941000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>516000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>228000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>658000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>97000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-790000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5375000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-946000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-374000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-444000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-775000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1938000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-496000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>164000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>214000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>483000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>10000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>341000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3310,215 +3385,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>402000</v>
+        <v>-134000</v>
       </c>
       <c r="E35" s="3">
-        <v>100000</v>
+        <v>428000</v>
       </c>
       <c r="F35" s="3">
-        <v>-724000</v>
+        <v>114000</v>
       </c>
       <c r="G35" s="3">
-        <v>1050000</v>
+        <v>-698000</v>
       </c>
       <c r="H35" s="3">
-        <v>733000</v>
+        <v>1064000</v>
       </c>
       <c r="I35" s="3">
-        <v>163000</v>
+        <v>759000</v>
       </c>
       <c r="J35" s="3">
+        <v>177000</v>
+      </c>
+      <c r="K35" s="3">
         <v>36000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>580000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>941000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>516000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>228000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>658000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>97000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-790000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5375000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-946000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-374000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-444000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-775000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1938000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-496000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>164000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>214000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>483000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>10000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>341000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3554,8 +3638,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3591,132 +3676,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9579000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9684000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10357000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8239000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6096000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7693000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5018000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4281000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4139000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5109000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5713000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5188000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5255000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5761000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6795000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6179000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8684000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8364000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10315000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4405000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4471000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4734000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5129000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4469000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4777000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2342000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>2169000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1487000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1173000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1122000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>873000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>828000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3793,132 +3882,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10038000</v>
+        <v>12505000</v>
       </c>
       <c r="E43" s="3">
-        <v>10195000</v>
+        <v>12832000</v>
       </c>
       <c r="F43" s="3">
-        <v>10189000</v>
+        <v>12901000</v>
       </c>
       <c r="G43" s="3">
-        <v>10288000</v>
+        <v>12865000</v>
       </c>
       <c r="H43" s="3">
-        <v>10448000</v>
+        <v>12977000</v>
       </c>
       <c r="I43" s="3">
-        <v>10656000</v>
+        <v>12788000</v>
       </c>
       <c r="J43" s="3">
+        <v>12566000</v>
+      </c>
+      <c r="K43" s="3">
         <v>10809000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15917000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16424000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16804000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>17278000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>17440000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16936000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6887000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6789000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6509000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6663000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7050000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6579000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6591000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6896000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6972000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7104000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7133000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7239000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3995,31 +4090,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>592000</v>
+        <v>4987000</v>
       </c>
       <c r="E45" s="3">
-        <v>866000</v>
+        <v>3643000</v>
       </c>
       <c r="F45" s="3">
-        <v>868000</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
+        <v>4322000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>5058000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>4322000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3319000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2296000</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
@@ -4057,29 +4155,29 @@
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X45" s="3">
         <v>958000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1110000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1262000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1170000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1263000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
@@ -4096,31 +4194,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>29960000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>28920000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>29933000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>28203000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>25445000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>25552000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>21763000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4197,132 +4298,138 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>109843000</v>
+        <v>106917000</v>
       </c>
       <c r="E47" s="3">
-        <v>104683000</v>
+        <v>101914000</v>
       </c>
       <c r="F47" s="3">
-        <v>104223000</v>
+        <v>97556000</v>
       </c>
       <c r="G47" s="3">
-        <v>99244000</v>
+        <v>96507000</v>
       </c>
       <c r="H47" s="3">
-        <v>99448000</v>
+        <v>92446000</v>
       </c>
       <c r="I47" s="3">
-        <v>97517000</v>
+        <v>94067000</v>
       </c>
       <c r="J47" s="3">
+        <v>93770000</v>
+      </c>
+      <c r="K47" s="3">
         <v>93878000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>94739000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>94890000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>99887000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>105306000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>102300000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>100895000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>106006000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>109087000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>105778000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>102693000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>96216000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>93340000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>94690000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>86853000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>82880000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>81281000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>79209000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>76822000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>516000</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4342,36 +4449,36 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S48" s="3">
         <v>691000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W48" s="3">
         <v>687000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>713000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>726000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>760000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4381,8 +4488,8 @@
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
@@ -4399,109 +4506,115 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5388000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5403000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5419000</v>
       </c>
-      <c r="F49" s="3">
-        <v>5433000</v>
-      </c>
       <c r="G49" s="3">
+        <v>5596000</v>
+      </c>
+      <c r="H49" s="3">
         <v>5448000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5463000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5478000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5482000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5635000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4721000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4723000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4728000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4734000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4739000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4744000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4737000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4745000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4756000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4760000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4751000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4765000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4776000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4769000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4780000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4791000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4802000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4601,8 +4714,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4702,109 +4818,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6924000</v>
+        <v>149693000</v>
       </c>
       <c r="E52" s="3">
-        <v>7549000</v>
+        <v>144608000</v>
       </c>
       <c r="F52" s="3">
-        <v>7270000</v>
+        <v>145865000</v>
       </c>
       <c r="G52" s="3">
-        <v>8208000</v>
+        <v>139200000</v>
       </c>
       <c r="H52" s="3">
-        <v>7957000</v>
+        <v>130314000</v>
       </c>
       <c r="I52" s="3">
-        <v>8145000</v>
+        <v>137412000</v>
       </c>
       <c r="J52" s="3">
+        <v>134070000</v>
+      </c>
+      <c r="K52" s="3">
         <v>8453000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9579000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9288000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8285000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6995000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6275000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5911000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6839000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6466000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6040000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6064000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7665000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7894000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5787000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6080000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6018000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6745000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6736000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7635000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4904,109 +5026,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>298989000</v>
+      </c>
+      <c r="E54" s="3">
         <v>287769000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>285577000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>276814000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>260252000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>269006000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>261500000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>252702000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>245600000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>253482000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>277658000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>292262000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>284579000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>285982000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>276832000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>275397000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>262496000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>254110000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>240781000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>249818000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>244646000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>238597000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>232819000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>220797000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>234451000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>231012000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5042,8 +5170,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5079,31 +5208,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5180,233 +5310,242 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8583000</v>
+        <v>127000</v>
       </c>
       <c r="E58" s="3">
-        <v>8298000</v>
+        <v>152000</v>
       </c>
       <c r="F58" s="3">
-        <v>8981000</v>
+        <v>147000</v>
       </c>
       <c r="G58" s="3">
-        <v>9001000</v>
+        <v>526000</v>
       </c>
       <c r="H58" s="3">
-        <v>8671000</v>
+        <v>113000</v>
       </c>
       <c r="I58" s="3">
-        <v>9415000</v>
+        <v>29000</v>
       </c>
       <c r="J58" s="3">
+        <v>751000</v>
+      </c>
+      <c r="K58" s="3">
         <v>9539000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7270000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6820000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5992000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6636000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7059000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8017000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9456000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5947000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5038000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4890000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4632000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4608000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4208000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1698000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1640000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2063000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2400000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2350000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4262000</v>
+        <v>16272000</v>
       </c>
       <c r="E59" s="3">
-        <v>4561000</v>
+        <v>15125000</v>
       </c>
       <c r="F59" s="3">
-        <v>5462000</v>
+        <v>13999000</v>
       </c>
       <c r="G59" s="3">
-        <v>4199000</v>
+        <v>10934000</v>
       </c>
       <c r="H59" s="3">
-        <v>5452000</v>
+        <v>8740000</v>
       </c>
       <c r="I59" s="3">
-        <v>4911000</v>
+        <v>9025000</v>
       </c>
       <c r="J59" s="3">
+        <v>6240000</v>
+      </c>
+      <c r="K59" s="3">
         <v>6189000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5316000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5786000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7007000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6264000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5706000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5962000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6802000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7845000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7260000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7447000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8366000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6060000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6068000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6146000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6321000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5032000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4687000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4714000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>17781000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>16116000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>15168000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>12692000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>9307000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>10576000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>7879000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5483,144 +5622,150 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10417000</v>
+        <v>5575000</v>
       </c>
       <c r="E61" s="3">
-        <v>10536000</v>
+        <v>5570000</v>
       </c>
       <c r="F61" s="3">
-        <v>10551000</v>
+        <v>5401000</v>
       </c>
       <c r="G61" s="3">
-        <v>11280000</v>
+        <v>5802000</v>
       </c>
       <c r="H61" s="3">
-        <v>12283000</v>
+        <v>5361000</v>
       </c>
       <c r="I61" s="3">
-        <v>12082000</v>
+        <v>5303000</v>
       </c>
       <c r="J61" s="3">
+        <v>4988000</v>
+      </c>
+      <c r="K61" s="3">
         <v>11278000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4026000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5698000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5318000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11848000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4772000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4867000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5105000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7321000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5916000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5915000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6336000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6403000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7086000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7144000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7299000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7455000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7306000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7422000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>269435000</v>
       </c>
       <c r="E62" s="3">
-        <v>239000</v>
+        <v>261610000</v>
       </c>
       <c r="F62" s="3">
-        <v>153000</v>
+        <v>260262000</v>
       </c>
       <c r="G62" s="3">
-        <v>216000</v>
+        <v>253162000</v>
       </c>
       <c r="H62" s="3">
-        <v>129000</v>
+        <v>241667000</v>
       </c>
       <c r="I62" s="3">
-        <v>158000</v>
+        <v>247336000</v>
       </c>
       <c r="J62" s="3">
+        <v>242549000</v>
+      </c>
+      <c r="K62" s="3">
         <v>108000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -5629,26 +5774,26 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>270000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>322000</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>679000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>724000</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5661,8 +5806,8 @@
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5685,8 +5830,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5786,8 +5934,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5887,8 +6038,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5988,109 +6142,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>286125000</v>
+        <v>292791000</v>
       </c>
       <c r="E66" s="3">
-        <v>283545000</v>
+        <v>283296000</v>
       </c>
       <c r="F66" s="3">
-        <v>274165000</v>
+        <v>280831000</v>
       </c>
       <c r="G66" s="3">
-        <v>258610000</v>
+        <v>271656000</v>
       </c>
       <c r="H66" s="3">
-        <v>265453000</v>
+        <v>256335000</v>
       </c>
       <c r="I66" s="3">
-        <v>257746000</v>
+        <v>263215000</v>
       </c>
       <c r="J66" s="3">
+        <v>255416000</v>
+      </c>
+      <c r="K66" s="3">
         <v>251301000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>242246000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>247893000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>269704000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>280743000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>272899000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>274250000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>266139000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>259821000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>245196000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>236516000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>220695000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>236362000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>229710000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>223754000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>219676000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>206931000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>222040000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>217674000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6126,8 +6286,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6227,8 +6388,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6328,8 +6492,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6376,13 +6543,13 @@
         <v>1562000</v>
       </c>
       <c r="R70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="S70" s="3">
         <v>1269000</v>
       </c>
       <c r="T70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="U70" s="3">
         <v>775000</v>
@@ -6391,7 +6558,7 @@
         <v>775000</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -6429,8 +6596,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6530,109 +6700,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9977000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10317000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10110000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10243000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11163000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10325000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9806000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9825000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10839000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10718000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9312000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8880000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8857000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8739000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8758000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10699000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12032000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12995000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17112000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11744000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12835000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13293000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13004000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13989000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12031000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12613000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6732,8 +6908,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6833,8 +7012,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6934,109 +7116,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1658000</v>
+      </c>
+      <c r="E76" s="3">
         <v>82000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>470000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1087000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>80000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1991000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2192000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-161000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1792000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4027000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6392000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9957000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10118000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10170000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9131000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14307000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16031000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16819000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19311000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12681000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14936000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14843000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13143000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13866000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12411000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13338000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7136,215 +7324,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>402000</v>
+        <v>-134000</v>
       </c>
       <c r="E81" s="3">
-        <v>100000</v>
+        <v>428000</v>
       </c>
       <c r="F81" s="3">
-        <v>-724000</v>
+        <v>114000</v>
       </c>
       <c r="G81" s="3">
-        <v>1050000</v>
+        <v>-698000</v>
       </c>
       <c r="H81" s="3">
-        <v>733000</v>
+        <v>1064000</v>
       </c>
       <c r="I81" s="3">
-        <v>163000</v>
+        <v>759000</v>
       </c>
       <c r="J81" s="3">
+        <v>177000</v>
+      </c>
+      <c r="K81" s="3">
         <v>36000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>580000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>941000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>516000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>228000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>658000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>97000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-790000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5375000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-946000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-374000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-444000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-775000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1938000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-496000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>164000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>214000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>483000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>10000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>341000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7380,109 +7577,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>189000</v>
+        <v>196000</v>
       </c>
       <c r="E83" s="3">
-        <v>240000</v>
+        <v>156000</v>
       </c>
       <c r="F83" s="3">
-        <v>236000</v>
+        <v>224000</v>
       </c>
       <c r="G83" s="3">
-        <v>196000</v>
+        <v>157000</v>
       </c>
       <c r="H83" s="3">
-        <v>156000</v>
+        <v>213000</v>
       </c>
       <c r="I83" s="3">
-        <v>224000</v>
+        <v>36000</v>
       </c>
       <c r="J83" s="3">
+        <v>142000</v>
+      </c>
+      <c r="K83" s="3">
         <v>227000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>216000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>191000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>180000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>161000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>88000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>95000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>153000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>89000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>162000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>176000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1330000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>93000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>131000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>433000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>239000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>104000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>-195000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>184000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>164000</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>8</v>
+      <c r="AG83" s="3">
+        <v>0</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7582,8 +7783,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7683,8 +7887,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7784,8 +7991,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7885,8 +8095,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7986,109 +8199,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>683000</v>
+      </c>
+      <c r="E89" s="3">
         <v>892000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-392000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>410000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>361000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-587000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>61000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>229000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>68000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-608000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-402000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>241000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-581000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-14000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-66000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>553000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-570000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>76000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>133000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-425000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-109000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>94000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>281000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-67000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>378000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>666000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>72000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8124,109 +8343,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-39000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-83000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-29000</v>
       </c>
       <c r="P91" s="3">
         <v>-29000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-23000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-63000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-14000</v>
       </c>
       <c r="U91" s="3">
         <v>-14000</v>
       </c>
       <c r="V91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-21000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-33000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-39000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8326,8 +8549,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8427,109 +8653,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2392000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2682000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>115000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-171000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>4147000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-993000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1348000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>459000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8565,92 +8797,93 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-78000</v>
+        <v>76000</v>
       </c>
       <c r="E96" s="3">
-        <v>-73000</v>
+        <v>78000</v>
       </c>
       <c r="F96" s="3">
+        <v>73000</v>
+      </c>
+      <c r="G96" s="3">
+        <v>74000</v>
+      </c>
+      <c r="H96" s="3">
+        <v>77000</v>
+      </c>
+      <c r="I96" s="3">
+        <v>78000</v>
+      </c>
+      <c r="J96" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-77000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-78000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-72000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-74000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-75000</v>
       </c>
       <c r="L96" s="3">
         <v>-75000</v>
       </c>
       <c r="M96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-70000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-72000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-74000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-74000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-75000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-76000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-77000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-69000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-70000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-74000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-141000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-68000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-69000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -8666,8 +8899,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8767,8 +9003,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8868,8 +9107,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8969,307 +9211,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3364000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4945000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2387000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>470000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3394000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2749000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3589000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1513000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1108000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1437000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2330000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1751000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3994000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4436000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1498000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5285000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>557000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2334000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>992000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4581000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3132000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>838000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-181000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>700000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-264000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>954000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>34000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>34000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>25000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>34000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-41000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-14000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>22000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>12000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-13000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>16000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-8000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-3000</v>
       </c>
       <c r="AA101" s="3">
         <v>-3000</v>
       </c>
       <c r="AB101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>8000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-992000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2284000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2135000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2674000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>742000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>301000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-970000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-604000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>525000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-506000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>669000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>320000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5886000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-263000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>265000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>660000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-308000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>742000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>259000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>533000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-593000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,445 +656,457 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3833000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2933000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3763000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2230000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1861000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3912000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2386000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2357000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4261000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3284000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2018000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3454000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3853000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3800000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4144000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3698000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4186000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3312000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3519000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3221000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3365000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3531000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6735000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3344000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3136000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3093000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3012000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1184000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1056000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1040000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1057000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>998000</v>
       </c>
       <c r="H9" s="3">
         <v>998000</v>
       </c>
       <c r="I9" s="3">
+        <v>998000</v>
+      </c>
+      <c r="J9" s="3">
         <v>959000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>963000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1500000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1395000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1305000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1559000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1461000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1492000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1534000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1612000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1441000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1682000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1345000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3431000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1490000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2372000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3028000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1465000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1376000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1021000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1455000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>876000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1974000</v>
+      </c>
+      <c r="E10" s="3">
         <v>227000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1423000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>857000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-510000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2268000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1069000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2761000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1889000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>713000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1895000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2392000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2308000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2610000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2086000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2745000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1630000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2174000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-210000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1875000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1159000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3707000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1879000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1760000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1557000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1131,8 +1143,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,8 +1355,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1365,8 +1384,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1384,94 +1403,97 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-5000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>58000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>31000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>38000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>7000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>25800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>27200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>35000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>24300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E15" s="3">
         <v>211000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>189000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>240000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>183000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>196000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>156000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>224000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1547,8 +1569,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1582,216 +1607,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2372000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3035000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2767000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1926000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2930000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2094000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1783000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2755000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2741000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2607000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2551000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2832000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2793000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2626000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2650000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2886000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2547000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2711000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2441000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5710000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2731000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3451000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5276000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2582000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2804000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1640000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2584000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1461000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-102000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>996000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>304000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1069000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1818000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>603000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-398000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1520000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>677000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-533000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>622000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1060000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1174000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1494000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>812000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1639000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>601000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1078000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>634000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>80000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1459000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>762000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>332000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1453000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>428000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>710000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>839000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>405000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>103000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>600000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1828,8 +1860,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1854,173 +1887,176 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>199000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1858000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>159000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-535000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-185000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9400000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-453000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2057000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>548000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1640000</v>
+      </c>
+      <c r="E21" s="3">
         <v>109000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1185000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>544000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-886000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2014000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>759000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-174000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>456000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1089000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1361000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>923000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>686000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1077000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>390000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-709000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8241000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-962000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-629000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2493000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-748000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>566000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>638000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2033,323 +2069,335 @@
       <c r="AI21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E22" s="3">
         <v>-88000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>315000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>57000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>-252000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>343000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>64000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>61000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>53000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>51000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>50000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>47000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>60000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>59000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>51000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>74000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>48000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>52000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>52000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>54000</v>
       </c>
       <c r="X22" s="3">
         <v>54000</v>
       </c>
       <c r="Y22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>113000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>56000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>60000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>65000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>60000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>45000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>42000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>35000</v>
       </c>
       <c r="AI22" s="3">
         <v>35000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AK22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1197000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>681000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>247000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-817000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1475000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>539000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-459000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>158000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>825000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1275000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>734000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>465000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>930000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>244000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-923000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6859000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-427000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-524000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-924000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2329000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-618000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>322000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>428000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>776000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>47000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>483000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-40000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>116000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>30000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-228000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>340000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-292000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-725000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>177000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>264000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>137000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>77000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>165000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-408000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-885000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-218000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1075000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1434000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-259000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-121000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-213000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-215000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>448000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-259000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>63000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>225000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>30000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2452,216 +2500,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1015000</v>
+      </c>
+      <c r="E26" s="3">
         <v>26000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>565000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>217000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-589000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1135000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>831000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>266000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>138000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>648000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1011000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>597000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>388000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>765000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>223000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-705000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5425000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-850000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-306000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-311000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-709000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1881000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-359000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>272000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>365000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>551000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>106000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>524000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>873000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-148000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>402000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>100000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-724000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1050000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>733000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>163000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>580000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>941000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>516000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>228000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>658000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>97000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-790000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5375000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-946000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-374000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-444000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-775000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1820000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>175000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>242000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>407000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>10000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>341000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2764,8 +2821,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2820,8 +2880,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2838,24 +2898,24 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>118000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-84000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>76000</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2868,8 +2928,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2972,8 +3035,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3076,8 +3142,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3102,190 +3171,196 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>1309000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-199000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-159000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>535000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>185000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1199000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2546000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3612000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1472000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6038000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1689000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>453000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1870000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1630000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2006000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>46000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>236000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>18000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>316000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>235000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>899000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-134000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>428000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>114000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-698000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1064000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>759000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>177000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>580000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>941000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>516000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>228000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>658000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>97000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-790000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5375000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-946000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-374000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-444000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-775000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1938000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-496000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>164000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>214000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>483000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>10000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>341000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3388,221 +3463,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>899000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-134000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>428000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>114000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-698000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1064000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>759000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>177000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>580000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>941000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>516000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>228000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>658000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>97000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-790000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5375000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-946000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-374000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-444000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-775000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1938000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-496000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>164000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>214000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>483000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>10000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>341000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3639,8 +3723,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3677,139 +3762,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6964000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9579000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9684000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10357000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8239000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6096000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7693000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5018000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4281000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4139000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5109000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5713000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5188000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5255000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5761000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6795000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6179000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8684000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8364000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10315000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4405000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4471000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4734000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5129000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4469000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4777000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1232000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2342000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2169000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1487000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1173000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1122000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>873000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>828000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3885,112 +3974,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12695000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12505000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12832000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12901000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12865000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12977000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12788000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12566000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10809000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15917000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16424000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16804000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>17278000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>17440000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16936000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6887000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6789000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6509000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6663000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7050000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6579000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6591000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6896000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6972000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7104000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7133000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7239000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4015,8 +4110,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4093,35 +4188,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6890000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4987000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3643000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4322000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5058000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4322000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3319000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2296000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4158,29 +4256,29 @@
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3">
         <v>958000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1110000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1262000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1170000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1263000</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
@@ -4197,35 +4295,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28281000</v>
+      </c>
+      <c r="E46" s="3">
         <v>29960000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28920000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29933000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28203000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25445000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25552000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21763000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4301,117 +4402,123 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>108325000</v>
+      </c>
+      <c r="E47" s="3">
         <v>106917000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>101914000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>97556000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>96507000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>92446000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>94067000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>93770000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>93878000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>94739000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>94890000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>99887000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>105306000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>102300000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>100895000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>106006000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>109087000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>105778000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>102693000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>96216000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>93340000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>94690000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>86853000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>82880000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>81281000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>79209000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>76822000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>8</v>
+      <c r="D48" s="3">
+        <v>618000</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>8</v>
@@ -4419,20 +4526,20 @@
       <c r="F48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3">
         <v>516000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4452,36 +4559,36 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T48" s="3">
         <v>691000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X48" s="3">
         <v>687000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>713000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>726000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>760000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4491,8 +4598,8 @@
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF48" s="3">
         <v>0</v>
@@ -4509,112 +4616,118 @@
       <c r="AJ48" s="3">
         <v>0</v>
       </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5493000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5388000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5403000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5419000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5596000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5448000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5463000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5478000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5482000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5635000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4721000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4723000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4728000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4734000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4739000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4744000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4737000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4745000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4756000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4760000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4751000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4765000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4776000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4769000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4780000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4791000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4802000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4717,8 +4830,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4821,112 +4937,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>145796000</v>
+      </c>
+      <c r="E52" s="3">
         <v>149693000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>144608000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>145865000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>139200000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>130314000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>137412000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>134070000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8453000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9579000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9288000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8285000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6995000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6275000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5911000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6839000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6466000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6040000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6064000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7665000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7894000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5787000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6080000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6018000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6745000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6736000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7635000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5029,112 +5151,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>295866000</v>
+      </c>
+      <c r="E54" s="3">
         <v>298989000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>287769000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>285577000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>276814000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>260252000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>269006000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>261500000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>252702000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>245600000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>253482000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>277658000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>292262000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>284579000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>285982000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>276832000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>275397000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>262496000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>254110000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>240781000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>249818000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>244646000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>238597000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>232819000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>220797000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>234451000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>231012000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5171,8 +5299,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5209,8 +5338,9 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5235,8 +5365,8 @@
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5313,243 +5443,252 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>238000</v>
+      </c>
+      <c r="E58" s="3">
         <v>127000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>152000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>147000</v>
       </c>
-      <c r="G58" s="3">
-        <v>526000</v>
-      </c>
       <c r="H58" s="3">
+        <v>370000</v>
+      </c>
+      <c r="I58" s="3">
         <v>113000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>29000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>751000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9539000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7270000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6820000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5992000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6636000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7059000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8017000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>9456000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5947000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5038000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4890000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4632000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4608000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4208000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1698000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1640000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2063000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2400000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2350000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17922000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16272000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15125000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13999000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10934000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8740000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9025000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6240000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6189000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5316000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5786000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7007000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6264000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5706000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5962000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6802000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7845000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7260000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7447000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8366000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6060000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6068000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6146000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6321000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5032000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4687000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4714000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18935000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17781000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16116000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15168000</v>
       </c>
-      <c r="G60" s="3">
-        <v>12692000</v>
-      </c>
       <c r="H60" s="3">
+        <v>12536000</v>
+      </c>
+      <c r="I60" s="3">
         <v>9307000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10576000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7879000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5625,150 +5764,156 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6544000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5575000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5570000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5401000</v>
       </c>
-      <c r="G61" s="3">
-        <v>5802000</v>
-      </c>
       <c r="H61" s="3">
+        <v>5958000</v>
+      </c>
+      <c r="I61" s="3">
         <v>5361000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5303000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4988000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11278000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4026000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5698000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5318000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11848000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4772000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4867000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5105000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7321000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5916000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5915000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6336000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6403000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7086000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7144000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7299000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7455000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7306000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7422000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>266819000</v>
+      </c>
+      <c r="E62" s="3">
         <v>269435000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>261610000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>260262000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>253162000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>241667000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>247336000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>242549000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>108000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -5777,26 +5922,26 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>270000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>322000</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>679000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>724000</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5809,8 +5954,8 @@
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5833,8 +5978,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5937,8 +6085,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6041,8 +6192,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6145,112 +6299,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>292298000</v>
+      </c>
+      <c r="E66" s="3">
         <v>292791000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>283296000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>280831000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>271656000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>256335000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>263215000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>255416000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>251301000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>242246000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>247893000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>269704000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>280743000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>272899000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>274250000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>266139000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>259821000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>245196000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>236516000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>220695000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>236362000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>229710000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>223754000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>219676000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>206931000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>222040000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>217674000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6287,8 +6447,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6391,8 +6552,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6495,13 +6659,16 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1562000</v>
+        <v>1507000</v>
       </c>
       <c r="E70" s="3">
         <v>1562000</v>
@@ -6546,13 +6713,13 @@
         <v>1562000</v>
       </c>
       <c r="S70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="T70" s="3">
         <v>1269000</v>
       </c>
       <c r="U70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="V70" s="3">
         <v>775000</v>
@@ -6561,7 +6728,7 @@
         <v>775000</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -6599,8 +6766,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6703,112 +6873,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10647000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9977000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10317000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10110000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10243000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11163000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10325000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9806000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9825000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10839000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10718000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9312000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8880000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8857000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8739000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8758000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10699000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12032000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12995000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17112000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11744000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12835000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13293000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13004000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13989000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12031000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12613000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6911,8 +7087,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7015,8 +7194,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7119,112 +7301,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1658000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>82000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>470000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1087000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>80000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1991000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2192000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-161000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1792000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4027000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6392000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9957000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10118000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10170000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9131000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14307000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16031000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16819000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19311000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12681000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14936000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14843000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13143000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13866000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12411000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13338000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7327,221 +7515,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>899000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-134000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>428000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>114000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-698000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1064000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>759000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>177000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>580000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>941000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>516000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>228000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>658000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>97000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-790000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5375000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-946000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-374000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-444000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-775000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1938000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-496000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>164000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>214000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>483000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>10000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>341000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7578,112 +7775,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E83" s="3">
         <v>196000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>156000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>224000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>157000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>213000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>36000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>142000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>227000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>216000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>191000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>180000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>161000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>88000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>95000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>153000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>89000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>162000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>176000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1330000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>93000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>131000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>433000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>239000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>104000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>-195000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>184000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>164000</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>8</v>
+      <c r="AH83" s="3">
+        <v>0</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7786,8 +7987,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7890,8 +8094,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7994,8 +8201,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8098,8 +8308,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8202,112 +8415,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400000</v>
+      </c>
+      <c r="E89" s="3">
         <v>683000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>892000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-392000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>410000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>361000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-587000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>61000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>229000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>68000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-608000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-402000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>241000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-581000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-14000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-66000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>553000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>22000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-570000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>76000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>133000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-425000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-109000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>94000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>281000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-67000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>378000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>666000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>72000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8344,112 +8563,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-35000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-65000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-83000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-29000</v>
       </c>
       <c r="Q91" s="3">
         <v>-29000</v>
       </c>
       <c r="R91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="S91" s="3">
         <v>-23000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-63000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-14000</v>
       </c>
       <c r="V91" s="3">
         <v>-14000</v>
       </c>
       <c r="W91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-21000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-39000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8552,8 +8775,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8656,112 +8882,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5536000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2392000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2682000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>115000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-171000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>4147000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-993000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1348000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>459000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8798,95 +9030,96 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E96" s="3">
         <v>76000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>78000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>73000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>74000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>77000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>78000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>72000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-75000</v>
       </c>
       <c r="M96" s="3">
         <v>-75000</v>
       </c>
       <c r="N96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-70000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-72000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-76000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-74000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-75000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-76000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-77000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-69000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-70000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-74000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-141000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-68000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-69000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -8902,8 +9135,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9006,8 +9242,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9110,8 +9349,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9214,316 +9456,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2549000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1583000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3364000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4945000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2387000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>470000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3394000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2749000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3589000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1513000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1108000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1437000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2330000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1751000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3994000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4436000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1498000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5285000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>557000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2334000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>992000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4581000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3132000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>838000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-181000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>700000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-264000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>954000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>34000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-38000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-41000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>34000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-38000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-41000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>22000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>12000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-13000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>16000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-3000</v>
       </c>
       <c r="AB101" s="3">
         <v>-3000</v>
       </c>
       <c r="AC101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>11000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2615000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-105000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-992000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2284000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2135000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2674000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>742000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>301000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-970000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-604000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>525000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-506000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>669000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>320000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5886000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-263000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>265000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>660000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-308000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>742000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>259000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>533000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-593000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,457 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4576000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3833000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2933000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3763000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2230000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1861000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3912000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2386000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2357000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4261000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3284000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2018000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3454000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3853000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3800000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4144000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3698000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4186000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3312000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3519000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3221000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3365000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3531000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6735000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3344000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3136000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3093000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3012000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1102000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1184000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1056000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1040000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1057000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>998000</v>
       </c>
       <c r="I9" s="3">
         <v>998000</v>
       </c>
       <c r="J9" s="3">
+        <v>998000</v>
+      </c>
+      <c r="K9" s="3">
         <v>959000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>963000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1500000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1395000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1305000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1559000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1461000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1492000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1534000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1612000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1441000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1682000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1345000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3431000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1490000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2372000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3028000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1465000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1376000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1021000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1455000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>876000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1179000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1974000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>227000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1423000</v>
       </c>
-      <c r="G10" s="3">
-        <v>857000</v>
-      </c>
       <c r="H10" s="3">
+        <v>828000</v>
+      </c>
+      <c r="I10" s="3">
         <v>-510000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2268000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1069000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2761000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1889000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>713000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1895000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2392000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2308000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2610000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2086000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2745000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1630000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2174000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-210000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1875000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1159000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3707000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1879000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1760000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1557000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1144,8 +1156,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1251,8 +1264,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1358,8 +1374,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,8 +1406,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1406,97 +1425,100 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-5000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>58000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>31000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>38000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>25800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>27200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>35000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>24300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E15" s="3">
         <v>179000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>211000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>189000</v>
       </c>
-      <c r="G15" s="3">
-        <v>240000</v>
-      </c>
       <c r="H15" s="3">
+        <v>241000</v>
+      </c>
+      <c r="I15" s="3">
         <v>183000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>196000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>156000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>224000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1572,8 +1594,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1608,222 +1633,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4347000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2372000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3035000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2767000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1926000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1954000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2930000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2094000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1783000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2755000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2741000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2607000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2551000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2832000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2793000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2626000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2650000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2886000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2547000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2711000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2441000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5710000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2731000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3451000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5276000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2582000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2804000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1640000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2584000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1461000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-102000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>996000</v>
       </c>
-      <c r="G18" s="3">
-        <v>304000</v>
-      </c>
       <c r="H18" s="3">
+        <v>276000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1069000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1818000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>603000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-398000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1520000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>677000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-533000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>622000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1060000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1174000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1494000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>812000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1639000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>601000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1078000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>634000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>80000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1459000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>762000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>332000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1453000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>428000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>710000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>839000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>405000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>103000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>600000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1861,8 +1893,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1890,176 +1923,179 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>199000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1858000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>159000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-535000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-185000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9400000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-453000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2057000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>548000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>442000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1640000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>109000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1185000</v>
       </c>
-      <c r="G21" s="3">
-        <v>544000</v>
-      </c>
       <c r="H21" s="3">
+        <v>517000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-886000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2014000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>759000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-174000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>456000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1089000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1361000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>923000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>686000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1077000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>390000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-709000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8241000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-962000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-242000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-629000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2493000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-748000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>566000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>638000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2072,332 +2108,344 @@
       <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E22" s="3">
         <v>264000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-88000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>315000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>57000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>-252000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>343000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>64000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>61000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>53000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>50000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>60000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>59000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>51000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>74000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>48000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>52000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>48000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>52000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>54000</v>
       </c>
       <c r="Y22" s="3">
         <v>54000</v>
       </c>
       <c r="Z22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>113000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>56000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>60000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>65000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>60000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>46000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>45000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>42000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>35000</v>
       </c>
       <c r="AJ22" s="3">
         <v>35000</v>
       </c>
       <c r="AK22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AL22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1197000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>681000</v>
       </c>
-      <c r="G23" s="3">
-        <v>247000</v>
-      </c>
       <c r="H23" s="3">
+        <v>219000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-817000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1475000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>539000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-459000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>158000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>825000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1275000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>734000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>465000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>930000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>244000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-923000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6859000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-427000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-524000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-924000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2329000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-618000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>322000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>428000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>776000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>47000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>483000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E24" s="3">
         <v>182000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-40000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>116000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-228000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>340000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-292000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>-725000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>177000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>264000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>137000</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>77000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>165000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-408000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-885000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>-1075000</v>
+      </c>
+      <c r="X24" s="3">
+        <v>1434000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>-259000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>-121000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>-213000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>-215000</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>448000</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>-259000</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>50000</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>63000</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>225000</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>30000</v>
       </c>
-      <c r="H24" s="3">
-        <v>-228000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>340000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-292000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-725000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>20000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>177000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>264000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>137000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>77000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>165000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>21000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-408000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-885000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-218000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-1075000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>1434000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>-259000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>-121000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-213000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-215000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>448000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>-259000</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>50000</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>63000</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>225000</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>-59000</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>-41000</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>30000</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,222 +2551,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1015000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>26000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>565000</v>
       </c>
-      <c r="G26" s="3">
-        <v>217000</v>
-      </c>
       <c r="H26" s="3">
+        <v>195000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-589000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1135000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>831000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>266000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>138000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>648000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1011000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>597000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>388000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>765000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>223000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-705000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5425000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-850000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-306000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-311000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-709000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1881000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-359000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>272000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>365000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>551000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>106000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>524000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E27" s="3">
         <v>873000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-148000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>402000</v>
       </c>
-      <c r="G27" s="3">
-        <v>100000</v>
-      </c>
       <c r="H27" s="3">
+        <v>78000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-724000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1050000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>733000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>163000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>580000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>941000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>516000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>228000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>658000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>97000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-790000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5375000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-946000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-374000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-444000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-775000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1820000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>175000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>242000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>407000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>341000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2824,8 +2881,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2883,8 +2943,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2901,24 +2961,24 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>118000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-84000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>76000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2931,8 +2991,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3038,8 +3101,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3145,8 +3211,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3174,193 +3243,199 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>1309000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-199000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-159000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>535000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>185000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1199000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2546000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3612000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1472000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6038000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1689000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>453000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1870000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1630000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2006000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>46000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>236000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>18000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>316000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>235000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E33" s="3">
         <v>899000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-134000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>428000</v>
       </c>
-      <c r="G33" s="3">
-        <v>114000</v>
-      </c>
       <c r="H33" s="3">
+        <v>92000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-698000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1064000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>759000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>177000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>580000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>941000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>516000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>228000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>658000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>97000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-790000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5375000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-946000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-374000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-444000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-775000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1938000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-496000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>164000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>214000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>483000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>10000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>341000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3466,227 +3541,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E35" s="3">
         <v>899000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-134000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>428000</v>
       </c>
-      <c r="G35" s="3">
-        <v>114000</v>
-      </c>
       <c r="H35" s="3">
+        <v>92000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-698000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1064000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>759000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>177000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>580000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>941000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>516000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>228000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>658000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>97000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-790000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5375000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-946000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-374000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-444000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-775000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1938000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-496000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>164000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>214000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>483000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>10000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>341000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3724,8 +3808,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3763,145 +3848,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8164000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6964000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9579000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9684000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10357000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8239000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6096000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7693000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5018000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4281000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4139000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5109000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5713000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5188000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5255000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5761000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6795000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6179000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8684000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8364000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10315000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4405000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4471000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4734000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5129000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4469000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4777000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1349000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1232000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2342000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2169000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1487000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1173000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1122000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>873000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>828000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3977,115 +4066,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11848000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12695000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12505000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12832000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12901000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12865000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12977000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12788000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12566000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10809000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15917000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16424000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16804000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>17278000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>17440000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16936000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6887000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6789000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6509000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6663000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7050000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6579000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6591000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6896000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6972000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7104000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7133000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7239000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4113,8 +4208,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4191,38 +4286,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7168000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6890000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4987000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3643000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4322000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5058000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4322000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3319000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2296000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4259,29 +4357,29 @@
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>958000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1110000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1262000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1170000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1263000</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG45" s="3">
         <v>0</v>
@@ -4298,38 +4396,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29301000</v>
+      </c>
+      <c r="E46" s="3">
         <v>28281000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29960000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28920000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29933000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28203000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25445000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25552000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21763000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4405,144 +4506,150 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>110391000</v>
+      </c>
+      <c r="E47" s="3">
         <v>108325000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>106917000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>101914000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>97556000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>96507000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>92446000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>94067000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>93770000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>93878000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>94739000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>94890000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>99887000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>105306000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>102300000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>100895000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>106006000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>109087000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>105778000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>102693000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>96216000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>93340000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>94690000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>86853000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>82880000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>81281000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>79209000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>76822000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>618000</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>516000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4562,36 +4669,36 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U48" s="3">
         <v>691000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y48" s="3">
         <v>687000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>713000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>726000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>760000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4601,8 +4708,8 @@
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF48" s="3">
-        <v>0</v>
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG48" s="3">
         <v>0</v>
@@ -4619,115 +4726,121 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5356000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5493000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5388000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5403000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5419000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5596000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5448000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5463000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5478000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5482000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5635000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4721000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4723000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4728000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4734000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4739000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4744000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4737000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4745000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4756000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4760000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4751000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4765000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4776000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4769000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4780000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4791000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4802000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4833,8 +4946,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4940,115 +5056,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>135056000</v>
+      </c>
+      <c r="E52" s="3">
         <v>145796000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>149693000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>144608000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>145865000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>139200000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>130314000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>137412000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>134070000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8453000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9579000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9288000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8285000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6995000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6275000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5911000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6839000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6466000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6040000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6064000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7665000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7894000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5787000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6080000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6018000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6745000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6736000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7635000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5154,115 +5276,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>287366000</v>
+      </c>
+      <c r="E54" s="3">
         <v>295866000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>298989000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>287769000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>285577000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>276814000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>260252000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>269006000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>261500000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>252702000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>245600000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>253482000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>277658000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>292262000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>284579000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>285982000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>276832000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>275397000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>262496000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>254110000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>240781000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>249818000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>244646000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>238597000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>232819000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>220797000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>234451000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>231012000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5300,8 +5428,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5339,8 +5468,9 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5368,8 +5498,8 @@
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5446,252 +5576,261 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E58" s="3">
         <v>238000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>127000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>152000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>147000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>370000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>113000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>29000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>751000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9539000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7270000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6820000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5992000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6636000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7059000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8017000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9456000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5947000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5038000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4890000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4632000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4608000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4208000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1698000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1640000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2063000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2400000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2350000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14616000</v>
+      </c>
+      <c r="E59" s="3">
         <v>17922000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16272000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15125000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13999000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10934000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8740000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9025000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6240000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6189000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5316000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5786000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7007000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6264000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5706000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5962000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6802000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7845000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7260000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7447000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8366000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6060000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6068000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6146000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6321000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5032000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4687000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4714000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15404000</v>
+      </c>
+      <c r="E60" s="3">
         <v>18935000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17781000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16116000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15168000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12536000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9307000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10576000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7879000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5767,156 +5906,162 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6440000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6544000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5575000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5570000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5401000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5958000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5361000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5303000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4988000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11278000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4026000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5698000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5318000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11848000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4772000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4867000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5105000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7321000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5916000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5915000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6336000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6403000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7086000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7144000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7299000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7455000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7306000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7422000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>261028000</v>
+      </c>
+      <c r="E62" s="3">
         <v>266819000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>269435000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>261610000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>260262000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>253162000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>241667000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>247336000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>242549000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>108000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -5925,26 +6070,26 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>270000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>322000</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
       <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
         <v>679000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>724000</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5957,8 +6102,8 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5981,8 +6126,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6088,8 +6236,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6195,8 +6346,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6302,115 +6456,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>282872000</v>
+      </c>
+      <c r="E66" s="3">
         <v>292298000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>292791000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>283296000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>280831000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>271656000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>256335000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>263215000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>255416000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>251301000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>242246000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>247893000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>269704000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>280743000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>272899000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>274250000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>266139000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>259821000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>245196000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>236516000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>220695000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>236362000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>229710000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>223754000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>219676000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>206931000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>222040000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>217674000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6448,8 +6608,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6555,8 +6716,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6662,8 +6826,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6671,7 +6838,7 @@
         <v>1507000</v>
       </c>
       <c r="E70" s="3">
-        <v>1562000</v>
+        <v>1507000</v>
       </c>
       <c r="F70" s="3">
         <v>1562000</v>
@@ -6716,13 +6883,13 @@
         <v>1562000</v>
       </c>
       <c r="T70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="U70" s="3">
         <v>1269000</v>
       </c>
       <c r="V70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="W70" s="3">
         <v>775000</v>
@@ -6731,7 +6898,7 @@
         <v>775000</v>
       </c>
       <c r="Y70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="Z70" s="3">
         <v>0</v>
@@ -6769,8 +6936,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6876,115 +7046,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10447000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10647000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9977000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10317000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10110000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10243000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11163000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10325000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9806000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9825000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10839000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10718000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9312000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8880000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8857000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8739000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8758000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10699000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12032000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12995000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>17112000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11744000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12835000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13293000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13004000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13989000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12031000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12613000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7090,8 +7266,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7197,8 +7376,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7304,115 +7486,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>894000</v>
+      </c>
+      <c r="E76" s="3">
         <v>78000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1658000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>82000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>470000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1087000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>80000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1991000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2192000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-161000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1792000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4027000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6392000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9957000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10118000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10170000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9131000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14307000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16031000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16819000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19311000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12681000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14936000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14843000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13143000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13866000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12411000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13338000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7518,227 +7706,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E81" s="3">
         <v>899000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-134000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>428000</v>
       </c>
-      <c r="G81" s="3">
-        <v>114000</v>
-      </c>
       <c r="H81" s="3">
+        <v>92000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-698000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1064000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>759000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>177000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>580000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>941000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>516000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>228000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>658000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>97000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-790000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5375000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-946000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-374000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-444000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-775000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1938000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-496000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>164000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>214000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>483000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>10000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>341000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7776,115 +7973,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E83" s="3">
         <v>125000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>196000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>156000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>224000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>157000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>213000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>36000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>142000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>227000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>216000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>191000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>180000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>161000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>88000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>95000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>153000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>89000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>162000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>176000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1330000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>93000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>131000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>433000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>239000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>104000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>-195000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>184000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>164000</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>8</v>
+      <c r="AI83" s="3">
+        <v>0</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7990,8 +8191,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8097,8 +8301,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8204,8 +8411,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8311,8 +8521,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8418,115 +8631,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E89" s="3">
         <v>400000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>683000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>892000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-392000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>410000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>361000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-587000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>61000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>229000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>68000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-608000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-402000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>241000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-581000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-14000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-66000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>553000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>22000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-570000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>76000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>133000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-425000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-109000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>94000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>281000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-67000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>378000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>666000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>72000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8564,115 +8783,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-63000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-35000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-65000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-83000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-29000</v>
       </c>
       <c r="R91" s="3">
         <v>-29000</v>
       </c>
       <c r="S91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-23000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-63000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-14000</v>
       </c>
       <c r="W91" s="3">
         <v>-14000</v>
       </c>
       <c r="X91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-33000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8778,8 +9001,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8885,115 +9111,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1199000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5536000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2392000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2682000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>115000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-171000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>4147000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-993000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1348000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>459000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9031,98 +9263,99 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E96" s="3">
         <v>75000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>76000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>78000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>73000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>74000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>77000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>78000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>72000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-75000</v>
       </c>
       <c r="N96" s="3">
         <v>-75000</v>
       </c>
       <c r="O96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-70000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-72000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-74000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-76000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-74000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-75000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-76000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-77000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-69000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-74000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-141000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-68000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-69000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -9138,8 +9371,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9245,8 +9481,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9352,8 +9591,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9459,325 +9701,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2228000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2549000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1583000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3364000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4945000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2387000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>470000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3394000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2749000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3589000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1513000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1108000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1437000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2330000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1751000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3994000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4436000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1498000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5285000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>557000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2334000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>992000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4581000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3132000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>838000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-181000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>700000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-264000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>954000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E101" s="3">
         <v>25000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>10000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>34000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-38000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-41000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>34000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-38000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-41000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>22000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>12000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-13000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>16000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-3000</v>
       </c>
       <c r="AC101" s="3">
         <v>-3000</v>
       </c>
       <c r="AD101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>11000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2615000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-105000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-992000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2284000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2135000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2674000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>742000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>301000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-970000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-604000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>525000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-506000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>669000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>320000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5886000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-263000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>265000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>660000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-308000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>742000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>259000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>533000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-593000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,469 +656,481 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2362000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4576000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3833000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2933000</v>
       </c>
-      <c r="G8" s="3">
-        <v>3763000</v>
-      </c>
       <c r="H8" s="3">
+        <v>3507000</v>
+      </c>
+      <c r="I8" s="3">
         <v>2230000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1861000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3912000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2386000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2357000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4261000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3284000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2018000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3454000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3853000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3800000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4144000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3698000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4186000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3312000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3519000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3221000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3365000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3531000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6735000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3344000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3136000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3093000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3012000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1080000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1102000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1184000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1056000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1040000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1057000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>998000</v>
       </c>
       <c r="J9" s="3">
         <v>998000</v>
       </c>
       <c r="K9" s="3">
+        <v>998000</v>
+      </c>
+      <c r="L9" s="3">
         <v>959000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>963000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1500000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1395000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1305000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1559000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1461000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1492000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1534000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1612000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1441000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1682000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1345000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3431000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1490000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2372000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3028000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1465000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1376000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1021000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1455000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>876000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1179000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1974000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>227000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1423000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="I10" s="3">
         <v>828000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-510000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2268000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1069000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2761000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1889000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>713000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1895000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2392000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2308000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2610000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2086000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2745000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1630000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2174000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-210000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1875000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1159000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3707000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1879000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1760000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1557000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1157,8 +1169,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1267,8 +1280,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1377,8 +1393,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,8 +1428,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1428,100 +1447,103 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-5000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-1000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>58000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>31000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>38000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>7000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>25800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>27200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>24300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E15" s="3">
         <v>213000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>179000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>211000</v>
       </c>
-      <c r="G15" s="3">
-        <v>189000</v>
-      </c>
       <c r="H15" s="3">
+        <v>193000</v>
+      </c>
+      <c r="I15" s="3">
         <v>241000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>183000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>196000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>156000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>224000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1597,8 +1619,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1634,228 +1659,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2664000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4347000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2372000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3035000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2767000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2764000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1954000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2930000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2094000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1783000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2755000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2741000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2607000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2551000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2832000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2793000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2626000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2650000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2886000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2547000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2711000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2441000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5710000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2731000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3451000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5276000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2582000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2804000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1640000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2584000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-302000</v>
+      </c>
+      <c r="E18" s="3">
         <v>229000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1461000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-102000</v>
       </c>
-      <c r="G18" s="3">
-        <v>996000</v>
-      </c>
       <c r="H18" s="3">
+        <v>743000</v>
+      </c>
+      <c r="I18" s="3">
         <v>276000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1069000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1818000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>603000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-398000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1520000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>677000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-533000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>622000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1060000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1174000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1494000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>812000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1639000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>601000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1078000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>634000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>80000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1459000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>762000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>332000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1453000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>428000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>710000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>839000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>405000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>103000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>600000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1894,8 +1926,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1926,179 +1959,182 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>199000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1858000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>159000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-535000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-185000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>9400000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-453000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2057000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>548000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-82000</v>
+      </c>
+      <c r="E21" s="3">
         <v>442000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1640000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>109000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1185000</v>
-      </c>
       <c r="H21" s="3">
+        <v>936000</v>
+      </c>
+      <c r="I21" s="3">
         <v>517000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-886000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2014000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>759000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-174000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>456000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1089000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1361000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>923000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>686000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1077000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>390000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-709000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8241000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-962000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-242000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-629000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2493000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-748000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>566000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>638000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2111,341 +2147,353 @@
       <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E22" s="3">
         <v>55000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>264000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>-88000</v>
       </c>
-      <c r="G22" s="3">
-        <v>315000</v>
-      </c>
       <c r="H22" s="3">
+        <v>62000</v>
+      </c>
+      <c r="I22" s="3">
         <v>57000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-252000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>343000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>64000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>61000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>53000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>51000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>47000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>60000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>59000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>51000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>74000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>52000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>48000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>52000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>54000</v>
       </c>
       <c r="Z22" s="3">
         <v>54000</v>
       </c>
       <c r="AA22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>113000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>56000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>60000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>65000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>60000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>46000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>45000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>42000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>35000</v>
       </c>
       <c r="AK22" s="3">
         <v>35000</v>
       </c>
       <c r="AL22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AM22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-363000</v>
+      </c>
+      <c r="E23" s="3">
         <v>174000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1197000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>681000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>219000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-817000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1475000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>539000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-459000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>158000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>825000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1275000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>734000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>465000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>930000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>244000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-923000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6859000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-427000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-524000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-924000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2329000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-618000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>322000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>428000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>776000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>47000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>483000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E24" s="3">
         <v>24000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>182000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-40000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>116000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-228000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>340000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-292000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-725000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>177000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>264000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>137000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>77000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>165000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-408000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-885000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-218000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1075000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1434000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-259000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-121000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-213000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-215000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>448000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-259000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>50000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>63000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>225000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>30000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,228 +2602,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-283000</v>
+      </c>
+      <c r="E26" s="3">
         <v>150000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1015000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>26000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>565000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>195000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-589000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1135000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>831000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>266000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>138000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>648000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1011000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>597000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>388000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>765000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>223000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-705000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5425000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-850000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-306000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-311000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-709000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1881000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-359000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>272000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>365000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>551000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>106000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>524000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-367000</v>
+      </c>
+      <c r="E27" s="3">
         <v>49000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>873000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-148000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>402000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>78000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-724000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1050000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>733000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>163000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>580000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>941000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>516000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>228000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>658000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>97000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-790000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5375000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-946000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-374000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-444000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-775000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1820000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>175000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>242000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>407000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>10000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>341000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2884,8 +2941,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2946,8 +3006,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2964,24 +3024,24 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>118000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-84000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>76000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2994,8 +3054,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3104,8 +3167,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3214,8 +3280,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3246,196 +3315,202 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>1309000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-199000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>535000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>185000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1199000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2546000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3612000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1472000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6038000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1689000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>453000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1870000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1630000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2006000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>46000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>236000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>18000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>316000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>235000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-349000</v>
+      </c>
+      <c r="E33" s="3">
         <v>63000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>899000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-134000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>428000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>92000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-698000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1064000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>759000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>177000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>580000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>941000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>516000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>228000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>658000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>97000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-790000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5375000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-946000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-374000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-444000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-775000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1938000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-496000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>164000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>214000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>483000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>10000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>341000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3544,233 +3619,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-349000</v>
+      </c>
+      <c r="E35" s="3">
         <v>63000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>899000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-134000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>428000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>92000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-698000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1064000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>759000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>177000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>580000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>941000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>516000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>228000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>658000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>97000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-790000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5375000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-946000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-374000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-444000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-775000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1938000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-496000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>164000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>214000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>483000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>10000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>341000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3809,8 +3893,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3849,151 +3934,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14957000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8164000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6964000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9579000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9684000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10357000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8239000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6096000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7693000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5018000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4281000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4139000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5109000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5713000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5188000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5255000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5761000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6795000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6179000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8684000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8364000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10315000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4405000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4471000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4734000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5129000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4469000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4777000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1399000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1349000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1232000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2342000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2169000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1487000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1173000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1122000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>873000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>828000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4069,118 +4158,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11923000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11848000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12695000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12505000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12832000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12901000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12865000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12977000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12788000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12566000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10809000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15917000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16424000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16804000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>17278000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>17440000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16936000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6887000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6789000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6509000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6663000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7050000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6579000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6591000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6896000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6972000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7104000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7133000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7239000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4211,8 +4306,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4289,41 +4384,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6411000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7168000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6890000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4987000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3643000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4322000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5058000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4322000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3319000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2296000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4360,29 +4458,29 @@
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>958000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1110000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1262000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1170000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1263000</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG45" s="3">
-        <v>0</v>
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH45" s="3">
         <v>0</v>
@@ -4399,41 +4497,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35173000</v>
+      </c>
+      <c r="E46" s="3">
         <v>29301000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28281000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29960000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28920000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29933000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28203000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25445000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25552000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21763000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4509,150 +4610,156 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>113988000</v>
+      </c>
+      <c r="E47" s="3">
         <v>110391000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>108325000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>106917000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>101914000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>97556000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>96507000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>92446000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>94067000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>93770000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>93878000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>94739000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>94890000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>99887000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>105306000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>102300000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>100895000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>106006000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>109087000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>105778000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>102693000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>96216000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>93340000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>94690000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>86853000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>82880000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>81281000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>79209000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>76822000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>618000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>516000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4672,36 +4779,36 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V48" s="3">
         <v>691000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z48" s="3">
         <v>687000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>713000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>726000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>760000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4711,8 +4818,8 @@
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG48" s="3">
-        <v>0</v>
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH48" s="3">
         <v>0</v>
@@ -4729,118 +4836,124 @@
       <c r="AL48" s="3">
         <v>0</v>
       </c>
+      <c r="AM48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5342000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5356000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5493000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5388000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5403000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5419000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5596000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5448000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5463000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5478000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5482000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5635000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4721000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4723000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4728000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4734000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4739000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4744000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4737000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4745000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4756000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4760000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4751000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4765000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4776000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4769000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4780000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4791000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4802000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4949,8 +5062,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5059,118 +5175,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>141224000</v>
+      </c>
+      <c r="E52" s="3">
         <v>135056000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>145796000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>149693000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>144608000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>145865000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>139200000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>130314000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>137412000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>134070000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8453000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9579000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9288000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8285000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6995000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6275000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5911000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6839000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6466000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6040000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6064000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7665000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7894000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5787000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6080000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6018000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6745000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6736000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7635000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5279,118 +5401,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>303088000</v>
+      </c>
+      <c r="E54" s="3">
         <v>287366000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>295866000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>298989000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>287769000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>285577000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>276814000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>260252000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>269006000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>261500000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>252702000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>245600000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>253482000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>277658000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>292262000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>284579000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>285982000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>276832000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>275397000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>262496000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>254110000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>240781000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>249818000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>244646000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>238597000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>232819000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>220797000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>234451000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>231012000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5429,8 +5557,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5469,8 +5598,9 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5501,8 +5631,8 @@
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -5579,261 +5709,270 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E58" s="3">
         <v>146000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>238000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>127000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>152000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>147000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>370000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>113000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>29000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>751000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9539000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7270000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6820000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5992000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6636000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7059000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8017000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>9456000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5947000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5038000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4890000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4632000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4608000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4208000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1698000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1640000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2063000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2400000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2350000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18316000</v>
+      </c>
+      <c r="E59" s="3">
         <v>14616000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17922000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16272000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15125000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13999000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10934000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8740000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9025000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6240000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6189000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5316000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5786000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7007000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6264000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5706000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5962000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6802000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7845000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7260000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7447000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8366000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6060000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6068000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6146000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6321000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5032000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4687000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4714000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19874000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15404000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18935000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17781000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16116000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15168000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12536000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9307000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10576000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7879000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5909,162 +6048,168 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6803000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6440000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6544000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5575000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5570000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5401000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5958000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5361000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5303000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4988000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11278000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4026000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5698000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5318000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11848000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4772000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4867000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5105000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7321000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5916000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5915000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6336000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6403000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7086000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7144000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7299000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7455000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7306000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7422000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>273448000</v>
+      </c>
+      <c r="E62" s="3">
         <v>261028000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>266819000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>269435000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>261610000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>260262000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>253162000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>241667000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>247336000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>242549000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>108000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -6073,26 +6218,26 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>270000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>322000</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
       <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>679000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>724000</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6105,8 +6250,8 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -6129,8 +6274,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6239,8 +6387,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6349,8 +6500,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6459,118 +6613,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>300125000</v>
+      </c>
+      <c r="E66" s="3">
         <v>282872000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>292298000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>292791000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>283296000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>280831000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>271656000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>256335000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>263215000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>255416000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>251301000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>242246000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>247893000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>269704000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>280743000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>272899000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>274250000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>266139000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>259821000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>245196000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>236516000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>220695000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>236362000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>229710000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>223754000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>219676000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>206931000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>222040000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>217674000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6609,8 +6769,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6719,8 +6880,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6829,19 +6993,22 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1507000</v>
+        <v>1228000</v>
       </c>
       <c r="E70" s="3">
         <v>1507000</v>
       </c>
       <c r="F70" s="3">
-        <v>1562000</v>
+        <v>1507000</v>
       </c>
       <c r="G70" s="3">
         <v>1562000</v>
@@ -6886,13 +7053,13 @@
         <v>1562000</v>
       </c>
       <c r="U70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="V70" s="3">
         <v>1269000</v>
       </c>
       <c r="W70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="X70" s="3">
         <v>775000</v>
@@ -6901,7 +7068,7 @@
         <v>775000</v>
       </c>
       <c r="Z70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="AA70" s="3">
         <v>0</v>
@@ -6939,8 +7106,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7049,118 +7219,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9870000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10447000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10647000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9977000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10317000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10110000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10243000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11163000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10325000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9806000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9825000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10839000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10718000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9312000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8880000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8857000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8739000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8758000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10699000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12032000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12995000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17112000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11744000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12835000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13293000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13004000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13989000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12031000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12613000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7269,8 +7445,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7379,8 +7558,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7489,118 +7671,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E76" s="3">
         <v>894000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>78000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1658000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>82000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>470000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1087000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>80000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1991000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2192000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-161000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1792000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4027000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6392000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9957000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10118000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10170000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9131000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14307000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16031000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16819000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19311000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12681000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14936000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14843000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13143000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13866000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12411000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13338000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7709,233 +7897,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-349000</v>
+      </c>
+      <c r="E81" s="3">
         <v>63000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>899000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-134000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>428000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>92000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-698000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1064000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>759000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>177000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>580000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>941000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>516000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>228000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>658000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>97000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-790000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5375000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-946000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-374000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-444000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-775000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1938000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-496000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>164000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>214000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>483000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>10000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>341000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7974,118 +8171,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E83" s="3">
         <v>241000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>125000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>196000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>156000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>224000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>157000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>213000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>142000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>227000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>216000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>191000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>180000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>161000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>88000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>95000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>153000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>89000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>162000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>176000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1330000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>93000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>131000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>433000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>239000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>104000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>-195000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>184000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>164000</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
       <c r="AI83" s="3">
         <v>0</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>8</v>
+      <c r="AJ83" s="3">
+        <v>0</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AL83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8194,8 +8395,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8304,8 +8508,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8414,8 +8621,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8524,8 +8734,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8634,118 +8847,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>341000</v>
+      </c>
+      <c r="E89" s="3">
         <v>158000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>400000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>683000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>892000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-392000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>410000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>361000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-587000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>61000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>229000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-608000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-402000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>241000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-581000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-14000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-66000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>553000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>22000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-570000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>76000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>133000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-425000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-109000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>94000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>281000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-67000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>378000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>666000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>72000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8784,118 +9003,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-35000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-65000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-83000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-29000</v>
       </c>
       <c r="S91" s="3">
         <v>-29000</v>
       </c>
       <c r="T91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-23000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-63000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-14000</v>
       </c>
       <c r="X91" s="3">
         <v>-14000</v>
       </c>
       <c r="Y91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9004,8 +9227,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9114,118 +9340,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2518000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1199000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5536000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2392000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2682000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>115000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-171000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>4147000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-993000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1348000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>459000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9264,101 +9496,102 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E96" s="3">
         <v>74000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>75000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>76000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>78000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>73000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>74000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>77000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>78000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>72000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-75000</v>
       </c>
       <c r="O96" s="3">
         <v>-75000</v>
       </c>
       <c r="P96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-72000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-74000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-76000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-74000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-75000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-76000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-77000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-69000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-74000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-68000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-69000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
@@ -9374,8 +9607,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9484,8 +9720,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9594,8 +9833,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9704,334 +9946,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8942000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2228000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2549000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1583000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3364000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4945000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2387000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>470000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3394000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2749000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3589000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1513000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1108000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1437000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2330000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1751000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3994000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4436000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1498000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5285000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>557000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2334000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>992000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4581000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3132000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>838000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-181000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>700000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-264000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>954000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>25000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-18000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>34000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-38000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-41000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>34000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-38000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-41000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-14000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>22000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>12000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>16000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>-3000</v>
       </c>
       <c r="AD101" s="3">
         <v>-3000</v>
       </c>
       <c r="AE101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>5000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>6000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>8000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6793000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1200000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2615000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-105000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-992000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2284000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2135000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2674000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>742000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>301000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-970000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-604000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>525000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-506000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>669000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>320000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5886000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-263000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>265000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>660000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-308000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>742000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>259000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>533000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-593000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,493 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3285000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1446000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2362000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4576000</v>
       </c>
-      <c r="G8" s="3">
-        <v>3833000</v>
-      </c>
       <c r="H8" s="3">
+        <v>3827000</v>
+      </c>
+      <c r="I8" s="3">
         <v>2930000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3760000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2230000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1861000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3912000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2386000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2357000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4261000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3284000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2018000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3454000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3853000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3800000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4144000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3698000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4186000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3312000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3519000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3221000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3365000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3531000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6735000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3344000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3136000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3093000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3012000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1207000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1138000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1080000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1102000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1184000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1194000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1056000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1040000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1057000</v>
-      </c>
-      <c r="K9" s="3">
-        <v>998000</v>
       </c>
       <c r="L9" s="3">
         <v>998000</v>
       </c>
       <c r="M9" s="3">
+        <v>998000</v>
+      </c>
+      <c r="N9" s="3">
         <v>959000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>963000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1500000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1395000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1305000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1559000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1461000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1492000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1534000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1612000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1441000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1682000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1345000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3431000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1490000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2372000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3028000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1465000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1376000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1021000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1455000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>876000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>868000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-851000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>125000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1179000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1974000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1964000</v>
+      </c>
+      <c r="I10" s="3">
         <v>230000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1424000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>828000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-510000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2268000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1069000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2761000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1889000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>713000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1895000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2392000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2308000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2610000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2086000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2745000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1630000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2174000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-210000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1875000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1159000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3707000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1879000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1760000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1557000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1183,8 +1195,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1299,8 +1312,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1415,8 +1431,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1453,8 +1472,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1472,106 +1491,109 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-5000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>58000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>31000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>38000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>25800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>27200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>35000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>1000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>24300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E15" s="3">
         <v>219000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>220000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>213000</v>
       </c>
-      <c r="G15" s="3">
-        <v>179000</v>
-      </c>
       <c r="H15" s="3">
+        <v>181000</v>
+      </c>
+      <c r="I15" s="3">
         <v>212000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>193000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>241000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>183000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>196000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>156000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>224000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1647,8 +1669,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1686,240 +1711,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2886000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2737000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2664000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4347000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2372000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2376000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3029000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2764000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1954000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2930000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2094000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1783000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2755000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2741000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2607000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2551000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2832000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2793000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2626000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2650000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2886000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2547000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2711000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2441000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5710000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2731000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3451000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5276000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2582000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2804000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1640000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2584000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>399000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1291000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-302000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>229000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1461000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-99000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>996000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>276000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1069000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1818000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>603000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-398000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1520000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>677000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-533000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>622000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1060000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1174000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1494000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>812000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1639000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>601000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1078000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>634000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>80000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1459000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>762000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>332000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1453000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>428000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>710000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>839000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>405000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>8000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>103000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>600000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1960,8 +1992,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1998,185 +2031,188 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>199000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1858000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>159000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-535000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-185000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9400000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-453000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2057000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>548000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1072000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-82000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>442000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1640000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1632000</v>
+      </c>
+      <c r="I21" s="3">
         <v>113000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1189000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>517000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-886000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2014000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>759000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-174000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>456000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1089000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1361000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>923000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>686000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1077000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>390000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-709000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8241000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-962000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-242000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-629000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2493000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-748000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>566000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>638000</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2189,359 +2225,371 @@
       <c r="AM21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E22" s="3">
         <v>57000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>61000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>55000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>264000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>-88000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>315000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>57000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>-252000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>343000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>64000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>61000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>53000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>51000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>50000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>47000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>60000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>59000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>51000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>74000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>48000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>52000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>48000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>52000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>54000</v>
       </c>
       <c r="AB22" s="3">
         <v>54000</v>
       </c>
       <c r="AC22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>113000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>56000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>60000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>65000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>60000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>46000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>42000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>35000</v>
       </c>
       <c r="AM22" s="3">
         <v>35000</v>
       </c>
       <c r="AN22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AO22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1348000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-363000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>174000</v>
       </c>
-      <c r="G23" s="3">
-        <v>1197000</v>
-      </c>
       <c r="H23" s="3">
+        <v>1187000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-11000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>681000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>219000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-817000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1475000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>539000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-459000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>158000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>825000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1275000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>734000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>465000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>930000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>244000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-923000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6859000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-427000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-524000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-924000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2329000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-618000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>322000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>428000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>776000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>47000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>483000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-133000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-80000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>24000</v>
       </c>
-      <c r="G24" s="3">
-        <v>182000</v>
-      </c>
       <c r="H24" s="3">
+        <v>179000</v>
+      </c>
+      <c r="I24" s="3">
         <v>-39000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>116000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>24000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-228000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>340000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-292000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-725000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>177000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>264000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>137000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>77000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>165000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>21000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-408000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-885000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-218000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1075000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1434000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-259000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-121000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-213000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-215000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>448000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-259000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>50000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>63000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>225000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>30000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2656,240 +2704,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1215000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-283000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>150000</v>
       </c>
-      <c r="G26" s="3">
-        <v>1015000</v>
-      </c>
       <c r="H26" s="3">
+        <v>1008000</v>
+      </c>
+      <c r="I26" s="3">
         <v>28000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>565000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>195000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-589000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1135000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>831000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>266000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>138000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>648000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1011000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>597000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>388000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>765000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>223000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-705000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5425000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-850000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-306000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-311000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-709000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1881000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-359000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>272000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>365000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>551000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>106000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>524000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1325000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-367000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>49000</v>
       </c>
-      <c r="G27" s="3">
-        <v>873000</v>
-      </c>
       <c r="H27" s="3">
+        <v>866000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-146000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>402000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>78000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-724000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1050000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>733000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>163000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>36000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>580000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>941000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>516000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>228000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>658000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>97000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-790000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5375000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-946000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-374000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-444000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-775000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1820000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>175000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>242000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>407000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>10000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>341000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3004,8 +3061,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3072,8 +3132,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -3090,24 +3150,24 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>118000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-84000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>76000</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3120,8 +3180,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3236,8 +3299,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3352,8 +3418,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3390,202 +3459,208 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>1309000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-199000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-159000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>535000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>185000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1199000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2546000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3612000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1472000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6038000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1689000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>453000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1870000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1630000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2006000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>46000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>236000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>316000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>235000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1309000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-349000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>63000</v>
       </c>
-      <c r="G33" s="3">
-        <v>899000</v>
-      </c>
       <c r="H33" s="3">
+        <v>892000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-132000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>428000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>92000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-698000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1064000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>759000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>177000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>36000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>580000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>941000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>516000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>228000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>658000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>97000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-790000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5375000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-946000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-374000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-444000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-775000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1938000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-496000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>164000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>214000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>483000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>10000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>341000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3700,245 +3775,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1309000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-349000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>63000</v>
       </c>
-      <c r="G35" s="3">
-        <v>899000</v>
-      </c>
       <c r="H35" s="3">
+        <v>892000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-132000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>428000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>92000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-698000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1064000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>759000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>177000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>36000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>580000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>941000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>516000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>228000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>658000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>97000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-790000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5375000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-946000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-374000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-444000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-775000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1938000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-496000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>164000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>214000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>483000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>10000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>341000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3979,8 +4063,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4021,163 +4106,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12462000</v>
+      </c>
+      <c r="E41" s="3">
         <v>13604000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14957000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8164000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6964000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9579000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9684000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10357000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8239000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6096000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7693000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5018000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4281000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4139000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5109000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5713000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5188000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5255000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5761000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6795000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6179000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8684000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8364000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10315000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4405000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4471000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4734000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5129000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4469000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4777000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1980000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1672000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1399000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1349000</v>
       </c>
-      <c r="G42" s="3">
-        <v>1232000</v>
-      </c>
       <c r="H42" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="I42" s="3">
         <v>2342000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2169000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1487000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1173000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1122000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>873000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>828000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4253,124 +4342,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25535000</v>
+      </c>
+      <c r="E43" s="3">
         <v>25005000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11923000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11848000</v>
       </c>
-      <c r="G43" s="3">
-        <v>12695000</v>
-      </c>
       <c r="H43" s="3">
+        <v>12556000</v>
+      </c>
+      <c r="I43" s="3">
         <v>12505000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12832000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12901000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12865000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12977000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12788000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12566000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10809000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15917000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16424000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16804000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>17278000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17440000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16936000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6887000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6789000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6509000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6663000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7050000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6579000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6591000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6896000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6972000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7104000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7133000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7239000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4407,8 +4502,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4485,47 +4580,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8566000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6968000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6411000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7168000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6890000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4987000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3643000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4322000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5058000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4322000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3319000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2296000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4562,29 +4660,29 @@
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>958000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1110000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1262000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1170000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1263000</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI45" s="3">
-        <v>0</v>
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ45" s="3">
         <v>0</v>
@@ -4601,47 +4699,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49042000</v>
+      </c>
+      <c r="E46" s="3">
         <v>47674000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35173000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29301000</v>
       </c>
-      <c r="G46" s="3">
-        <v>28281000</v>
-      </c>
       <c r="H46" s="3">
+        <v>28136000</v>
+      </c>
+      <c r="I46" s="3">
         <v>29960000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28920000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29933000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28203000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25445000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25552000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21763000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4717,129 +4818,135 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>110458000</v>
+      </c>
+      <c r="E47" s="3">
         <v>107865000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>113988000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>110391000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>108325000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>106917000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>101914000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>97556000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>96507000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>92446000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>94067000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>93770000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>93878000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>94739000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>94890000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>99887000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>105306000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>102300000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>100895000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>106006000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>109087000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>105778000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>102693000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>96216000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>93340000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>94690000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>86853000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>82880000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>81281000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>79209000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>76822000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>8</v>
+      <c r="D48" s="3">
+        <v>631000</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>8</v>
@@ -4847,32 +4954,32 @@
       <c r="F48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3">
         <v>618000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="3">
         <v>516000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -4892,36 +4999,36 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X48" s="3">
         <v>691000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB48" s="3">
         <v>687000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>713000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>726000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>760000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4931,8 +5038,8 @@
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI48" s="3">
-        <v>0</v>
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ48" s="3">
         <v>0</v>
@@ -4949,124 +5056,130 @@
       <c r="AN48" s="3">
         <v>0</v>
       </c>
+      <c r="AO48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5387000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5327000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5342000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5356000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5493000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5388000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5403000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5419000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5596000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5448000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5463000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5478000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5482000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5635000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4721000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4723000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4728000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4734000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4739000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4744000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4737000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4745000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4756000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4760000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4751000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4765000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4776000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4769000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4780000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4791000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4802000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5181,8 +5294,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5297,124 +5413,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>144784000</v>
+      </c>
+      <c r="E52" s="3">
         <v>146113000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>141224000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>135056000</v>
       </c>
-      <c r="G52" s="3">
-        <v>145796000</v>
-      </c>
       <c r="H52" s="3">
+        <v>145802000</v>
+      </c>
+      <c r="I52" s="3">
         <v>149693000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>144608000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>145865000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>139200000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>130314000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>137412000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>134070000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8453000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9579000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9288000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8285000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6995000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6275000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5911000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6839000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6466000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6040000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6064000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7665000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7894000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5787000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6080000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6018000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6745000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6736000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7635000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5529,124 +5651,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>317990000</v>
+      </c>
+      <c r="E54" s="3">
         <v>314409000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>303088000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>287366000</v>
       </c>
-      <c r="G54" s="3">
-        <v>295866000</v>
-      </c>
       <c r="H54" s="3">
+        <v>295727000</v>
+      </c>
+      <c r="I54" s="3">
         <v>298989000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>287769000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>285577000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>276814000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>260252000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>269006000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>261500000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>252702000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>245600000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>253482000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>277658000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>292262000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>284579000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>285982000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>276832000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>275397000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>262496000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>254110000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>240781000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>249818000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>244646000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>238597000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>232819000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>220797000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>234451000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>231012000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5687,8 +5815,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5729,8 +5858,9 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5767,8 +5897,8 @@
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -5845,279 +5975,288 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E58" s="3">
         <v>77000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>104000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>146000</v>
       </c>
-      <c r="G58" s="3">
-        <v>238000</v>
-      </c>
       <c r="H58" s="3">
+        <v>137000</v>
+      </c>
+      <c r="I58" s="3">
         <v>127000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>152000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>147000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>370000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>113000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>29000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>751000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9539000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7270000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6820000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5992000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6636000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7059000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8017000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9456000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5947000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5038000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4890000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4632000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4608000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4208000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1698000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1640000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2063000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2400000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2350000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21970000</v>
+      </c>
+      <c r="E59" s="3">
         <v>21307000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18316000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14616000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17922000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16272000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15125000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13999000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10934000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8740000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9025000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6240000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6189000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5316000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5786000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7007000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6264000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5706000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5962000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6802000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7845000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7260000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7447000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8366000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6060000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6068000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6146000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6321000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5032000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4687000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4714000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23880000</v>
+      </c>
+      <c r="E60" s="3">
         <v>22751000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19874000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15404000</v>
       </c>
-      <c r="G60" s="3">
-        <v>18935000</v>
-      </c>
       <c r="H60" s="3">
+        <v>18834000</v>
+      </c>
+      <c r="I60" s="3">
         <v>17781000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16116000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15168000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12536000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9307000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10576000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7879000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6193,174 +6332,180 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7142000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6363000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6803000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6440000</v>
       </c>
-      <c r="G61" s="3">
-        <v>6544000</v>
-      </c>
       <c r="H61" s="3">
+        <v>6645000</v>
+      </c>
+      <c r="I61" s="3">
         <v>5575000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5570000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5401000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5958000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5361000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5303000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4988000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11278000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4026000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5698000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5318000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11848000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4772000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4867000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5105000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7321000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5916000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5915000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6336000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6403000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7086000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7144000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7299000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7455000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7306000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7422000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
       <c r="AM61" s="3">
         <v>0</v>
       </c>
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>285180000</v>
+      </c>
+      <c r="E62" s="3">
         <v>283347000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>273448000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>261028000</v>
       </c>
-      <c r="G62" s="3">
-        <v>266819000</v>
-      </c>
       <c r="H62" s="3">
+        <v>266700000</v>
+      </c>
+      <c r="I62" s="3">
         <v>269435000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>261610000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>260262000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>253162000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>241667000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>247336000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>242549000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>108000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -6369,26 +6514,26 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>270000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>322000</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
       <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>679000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>724000</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6401,8 +6546,8 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH62" s="3">
         <v>0</v>
@@ -6425,8 +6570,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6541,8 +6689,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6657,8 +6808,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6773,124 +6927,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>316202000</v>
+      </c>
+      <c r="E66" s="3">
         <v>312461000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>300125000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>282872000</v>
       </c>
-      <c r="G66" s="3">
-        <v>292298000</v>
-      </c>
       <c r="H66" s="3">
+        <v>292179000</v>
+      </c>
+      <c r="I66" s="3">
         <v>292791000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>283296000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>280831000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>271656000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>256335000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>263215000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>255416000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>251301000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>242246000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>247893000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>269704000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>280743000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>272899000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>274250000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>266139000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>259821000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>245196000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>236516000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>220695000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>236362000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>229710000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>223754000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>219676000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>206931000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>222040000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>217674000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6931,8 +7091,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7047,8 +7208,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7163,8 +7327,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7172,16 +7339,16 @@
         <v>1068000</v>
       </c>
       <c r="E70" s="3">
+        <v>1068000</v>
+      </c>
+      <c r="F70" s="3">
         <v>1228000</v>
-      </c>
-      <c r="F70" s="3">
-        <v>1507000</v>
       </c>
       <c r="G70" s="3">
         <v>1507000</v>
       </c>
       <c r="H70" s="3">
-        <v>1562000</v>
+        <v>1507000</v>
       </c>
       <c r="I70" s="3">
         <v>1562000</v>
@@ -7226,13 +7393,13 @@
         <v>1562000</v>
       </c>
       <c r="W70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="X70" s="3">
         <v>1269000</v>
       </c>
       <c r="Y70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="Z70" s="3">
         <v>775000</v>
@@ -7241,7 +7408,7 @@
         <v>775000</v>
       </c>
       <c r="AB70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
@@ -7279,8 +7446,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7395,124 +7565,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8366000</v>
+      </c>
+      <c r="E72" s="3">
         <v>8360000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9870000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10447000</v>
       </c>
-      <c r="G72" s="3">
-        <v>10647000</v>
-      </c>
       <c r="H72" s="3">
+        <v>10627000</v>
+      </c>
+      <c r="I72" s="3">
         <v>9977000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10317000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10110000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10243000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11163000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10325000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9806000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9825000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10839000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10718000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9312000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8880000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8857000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8739000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8758000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10699000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12032000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12995000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17112000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11744000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12835000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13293000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13004000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13989000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12031000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12613000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7627,8 +7803,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7743,8 +7922,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7859,124 +8041,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1142000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-920000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-79000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>894000</v>
       </c>
-      <c r="G76" s="3">
-        <v>78000</v>
-      </c>
       <c r="H76" s="3">
+        <v>58000</v>
+      </c>
+      <c r="I76" s="3">
         <v>1658000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>82000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>470000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1087000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>80000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1991000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2192000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-161000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1792000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4027000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6392000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9957000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10118000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10170000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9131000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14307000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16031000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16819000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19311000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12681000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14936000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14843000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13143000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13866000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12411000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13338000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8091,245 +8279,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1309000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-349000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>63000</v>
       </c>
-      <c r="G81" s="3">
-        <v>899000</v>
-      </c>
       <c r="H81" s="3">
+        <v>892000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-132000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>428000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>92000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-698000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1064000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>759000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>177000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>36000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>580000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>941000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>516000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>228000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>658000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>97000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-790000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5375000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-946000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-374000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-444000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-775000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1938000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-496000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>164000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>214000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>483000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>10000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>341000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8370,124 +8567,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E83" s="3">
         <v>212000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>193000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>241000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>125000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>196000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>156000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>224000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>157000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>213000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>142000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>227000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>216000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>191000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>180000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>161000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>88000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>95000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>153000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>89000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>162000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>176000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1330000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>93000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>131000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>433000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>239000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>104000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>-195000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>184000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>164000</v>
       </c>
-      <c r="AI83" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
       <c r="AK83" s="3">
         <v>0</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>8</v>
+      <c r="AL83" s="3">
+        <v>0</v>
       </c>
       <c r="AM83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AN83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8602,8 +8803,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8718,8 +8922,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8834,8 +9041,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8950,8 +9160,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9066,124 +9279,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="E89" s="3">
         <v>369000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>341000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>158000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>683000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>892000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>31000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-392000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>410000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>361000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-587000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>61000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>229000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>68000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-608000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-402000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>241000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-581000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-14000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-66000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>553000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>22000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-570000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>76000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>133000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-425000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-109000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>94000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>281000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-67000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>378000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>666000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>72000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9224,124 +9443,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-63000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-35000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-39000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-65000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-29000</v>
       </c>
       <c r="U91" s="3">
         <v>-29000</v>
       </c>
       <c r="V91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-23000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-63000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-14000</v>
       </c>
       <c r="Z91" s="3">
         <v>-14000</v>
       </c>
       <c r="AA91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9456,8 +9679,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9572,124 +9798,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2483000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4768000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2518000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1199000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5536000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2392000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2682000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>115000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-171000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>4147000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-993000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1348000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>459000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9730,107 +9962,108 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E96" s="3">
         <v>81000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>82000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>74000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>75000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>76000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>78000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>73000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>74000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>77000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>78000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>72000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-75000</v>
       </c>
       <c r="Q96" s="3">
         <v>-75000</v>
       </c>
       <c r="R96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-70000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-72000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-74000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-76000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-74000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-75000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-76000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-77000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-69000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-74000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-141000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-68000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-69000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -9846,8 +10079,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9962,8 +10198,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10078,8 +10317,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10194,352 +10436,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1494000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3052000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8942000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2228000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2549000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1583000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3364000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4945000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2387000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>470000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3394000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2749000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3589000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1108000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1437000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2330000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1751000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3994000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4436000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1498000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5285000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>557000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2334000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>992000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4581000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3132000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>838000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-181000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>700000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-264000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>954000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E101" s="3">
         <v>21000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>25000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-18000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>34000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-38000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-41000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>34000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-41000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-14000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>22000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>12000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>16000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-3000</v>
       </c>
       <c r="AF101" s="3">
         <v>-3000</v>
       </c>
       <c r="AG101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>11000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>8000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1142000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1353000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6793000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1200000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2615000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-105000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-992000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2284000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2135000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2674000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>742000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>301000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-970000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-604000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>525000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-506000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>669000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>320000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5886000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-263000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>265000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>660000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-308000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>742000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>259000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>533000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-593000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>EQH</t>
   </si>
@@ -656,505 +656,517 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4230000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3285000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1446000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2362000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4576000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3827000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2930000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3760000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2230000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1861000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3912000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2386000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2357000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4261000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3284000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2018000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3454000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3853000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3800000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4144000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3698000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4186000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3312000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3519000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3221000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3365000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3531000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6735000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3344000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3136000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3093000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3012000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3110000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2940000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3123000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6198000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3066000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2586000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2919000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1207000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1138000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1080000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1102000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1194000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1056000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1040000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1057000</v>
-      </c>
-      <c r="L9" s="3">
-        <v>998000</v>
       </c>
       <c r="M9" s="3">
         <v>998000</v>
       </c>
       <c r="N9" s="3">
+        <v>998000</v>
+      </c>
+      <c r="O9" s="3">
         <v>959000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>963000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1500000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1395000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1305000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1559000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1461000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1492000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1534000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1612000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1441000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1682000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1345000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3431000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1490000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2372000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3028000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1465000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1376000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1021000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1455000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1156000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1139000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1720000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4106000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1734000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>876000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1351000</v>
+      </c>
+      <c r="E10" s="3">
         <v>868000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-851000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>125000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1179000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1964000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>230000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1424000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>828000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-510000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2268000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1069000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2761000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1889000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>713000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1895000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2392000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2308000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2610000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2086000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2745000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1630000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2174000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-210000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1875000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1159000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3707000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1879000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1760000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1557000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1954000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1801000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1403000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2092000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1332000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1710000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1538000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1196,8 +1208,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1315,8 +1328,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1434,8 +1450,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1475,8 +1494,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1494,109 +1513,112 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-5000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-1000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>58000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>31000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>38000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>4000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>25800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>27200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>35000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>1000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>24300</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E15" s="3">
         <v>185000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>219000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>220000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>213000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>181000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>212000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>193000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>241000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>183000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>196000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>156000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>224000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1694,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1712,246 +1737,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3281000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2886000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2737000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2664000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4347000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2376000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3029000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2764000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1954000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2930000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2094000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1783000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2755000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2741000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2607000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2551000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2832000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2793000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2626000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2650000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2886000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2547000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2711000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2441000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5710000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2731000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3451000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5276000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2582000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2804000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1640000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2584000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2400000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2101000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2718000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6190000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2963000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2249000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>949000</v>
+      </c>
+      <c r="E18" s="3">
         <v>399000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1291000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-302000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>229000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1451000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-99000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>996000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>276000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1069000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1818000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>603000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-398000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1520000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>677000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-533000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>622000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1060000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1174000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1494000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>812000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1639000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>601000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1078000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2489000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>634000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>80000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1459000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>762000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>332000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1453000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>428000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>710000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>839000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>405000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>8000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>103000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>600000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1993,8 +2025,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2034,188 +2067,191 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>199000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1858000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>159000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-535000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-185000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1199000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2546000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3612000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1472000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6038000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9400000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1689000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-453000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1870000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1630000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2057000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2006000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-236000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-316000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>548000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-235000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-660000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1173000</v>
+      </c>
+      <c r="E21" s="3">
         <v>584000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1072000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-82000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>442000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1632000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>113000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1189000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>517000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-886000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2014000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>759000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-174000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>456000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1089000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1361000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>923000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>686000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1077000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>390000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1581000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1884000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-709000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4784000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8241000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-962000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-242000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>22000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-629000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2493000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-748000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>566000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>638000</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2228,368 +2264,380 @@
       <c r="AN21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AO21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E22" s="3">
         <v>55000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>61000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>55000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>264000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-88000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>315000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>57000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>-252000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>343000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>64000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>61000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>53000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>51000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>47000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>60000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>59000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>51000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>74000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>48000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>52000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>48000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>52000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>54000</v>
       </c>
       <c r="AC22" s="3">
         <v>54000</v>
       </c>
       <c r="AD22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>113000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>56000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>60000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>65000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>60000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>45000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>42000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>73000</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>35000</v>
       </c>
       <c r="AN22" s="3">
         <v>35000</v>
       </c>
       <c r="AO22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AP22" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>887000</v>
+      </c>
+      <c r="E23" s="3">
         <v>344000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1348000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-363000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>174000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1187000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>681000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>219000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-817000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1475000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>539000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-459000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>158000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>825000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1275000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>734000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>465000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>930000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>244000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1808000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2021000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-923000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5008000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6859000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1109000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-427000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-524000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-924000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2329000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-618000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>322000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>428000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>776000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>47000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>483000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-167000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-472000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E24" s="3">
         <v>33000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-133000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-80000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>24000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>179000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-39000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>116000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>24000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-228000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>340000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-292000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-725000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>177000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>264000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>137000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>77000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>165000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>21000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-408000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-885000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-218000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1075000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1434000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-259000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-121000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-213000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-215000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>448000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-259000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>50000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>63000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>225000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>30000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-253000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,246 +2755,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>731000</v>
+      </c>
+      <c r="E26" s="3">
         <v>311000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1215000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-283000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>150000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1008000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>565000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>195000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-589000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1135000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>831000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>266000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>138000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>648000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1011000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>597000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>388000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>765000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>223000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1400000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1136000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-705000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3933000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5425000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-850000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-306000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-311000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-709000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1881000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-359000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>272000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>365000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>551000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>106000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>524000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-197000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-219000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>607000</v>
+      </c>
+      <c r="E27" s="3">
         <v>202000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1325000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-367000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>49000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>866000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-146000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>402000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>78000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-724000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1050000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>733000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>163000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>36000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>580000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>941000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>516000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>228000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>658000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>97000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1501000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-790000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4029000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5375000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-946000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-374000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-444000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-775000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1820000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>175000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>242000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>407000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>10000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>341000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-290000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-366000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3064,8 +3121,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3135,8 +3195,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3153,24 +3213,24 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>118000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-84000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>76000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3183,8 +3243,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3302,8 +3365,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3421,8 +3487,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3462,205 +3531,211 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1309000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-199000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1858000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-159000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>535000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>185000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1199000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2546000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3612000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1472000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6038000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9400000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1689000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>453000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1870000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1630000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2057000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2006000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>46000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>236000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>18000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>316000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-548000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>235000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1037000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>660000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>621000</v>
+      </c>
+      <c r="E33" s="3">
         <v>215000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1309000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-349000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>63000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>892000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-132000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>428000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>92000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-698000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1064000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>759000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>177000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>36000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>580000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>941000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>516000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>228000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>658000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>97000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1501000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-790000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4029000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5375000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-946000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-374000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-444000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-775000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1938000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-496000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>164000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>214000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>483000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>10000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>341000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-290000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-366000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3778,251 +3853,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>621000</v>
+      </c>
+      <c r="E35" s="3">
         <v>215000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1309000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-349000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>63000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>892000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-132000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>428000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>92000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-698000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1064000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>759000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>177000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>36000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>580000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>941000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>516000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>228000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>658000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>97000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1501000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-790000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4029000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5375000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-946000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-374000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-444000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-775000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1938000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-496000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>164000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>214000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>483000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>10000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>341000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-290000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-366000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4064,8 +4148,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4107,169 +4192,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9904000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12462000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13604000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14957000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8164000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6964000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9579000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9684000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10357000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8239000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6096000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7693000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5018000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4281000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4139000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5109000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5713000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5188000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5255000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5761000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6795000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6179000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8684000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8364000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10315000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4405000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4471000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4734000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5129000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4469000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4777000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6091000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4814000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6446000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6187000</v>
       </c>
-      <c r="AM41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1944000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1980000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1672000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1399000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1349000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1226000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2342000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2169000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1487000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1173000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1122000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>873000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>828000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4345,127 +4434,133 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25833000</v>
+      </c>
+      <c r="E43" s="3">
         <v>25535000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25005000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11923000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11848000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12556000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12505000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12832000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12901000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12865000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12977000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12788000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12566000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10809000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15917000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16424000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16804000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17278000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17440000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16936000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6887000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6789000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6509000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6663000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7050000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6579000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6591000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6896000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6972000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7104000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7133000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7239000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7253000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7181000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7241000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>7352000</v>
       </c>
-      <c r="AM43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4505,8 +4600,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4583,50 +4678,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7658000</v>
+      </c>
+      <c r="E45" s="3">
         <v>8566000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6968000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6411000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7168000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6890000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4987000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3643000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4322000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5058000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4322000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3319000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2296000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4663,29 +4761,29 @@
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3">
         <v>958000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1110000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1262000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1170000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1263000</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ45" s="3">
-        <v>0</v>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK45" s="3">
         <v>0</v>
@@ -4702,50 +4800,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>45690000</v>
+      </c>
+      <c r="E46" s="3">
         <v>49042000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>47674000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35173000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29301000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28136000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29960000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>28920000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29933000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28203000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25445000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25552000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21763000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4821,168 +4922,174 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>112077000</v>
+      </c>
+      <c r="E47" s="3">
         <v>110458000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>107865000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>113988000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>110391000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>108325000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>106917000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>101914000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>97556000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>96507000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>92446000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>94067000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>93770000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>93878000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>94739000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>94890000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>99887000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>105306000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>102300000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>100895000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>106006000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>109087000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>105778000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>102693000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>96216000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>93340000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>94690000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>86853000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>82880000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>81281000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>79209000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>76822000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>79941000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>82706000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>79455000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>77837000</v>
       </c>
-      <c r="AM47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>631000</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>618000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="3">
         <v>516000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -5002,36 +5109,36 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y48" s="3">
         <v>691000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC48" s="3">
         <v>687000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>713000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>726000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>760000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5041,8 +5148,8 @@
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ48" s="3">
-        <v>0</v>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK48" s="3">
         <v>0</v>
@@ -5059,127 +5166,133 @@
       <c r="AO48" s="3">
         <v>0</v>
       </c>
+      <c r="AP48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5350000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5387000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5327000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5342000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5356000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5493000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5388000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5403000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5419000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5596000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5448000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5463000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5478000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5482000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5635000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4721000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4723000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4728000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4734000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4739000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4744000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4737000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4745000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4756000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4760000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4751000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4765000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4776000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4769000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4780000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4791000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4802000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4813000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4824000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4840000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4852000</v>
       </c>
-      <c r="AM49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5297,8 +5410,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5416,127 +5532,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>139681000</v>
+      </c>
+      <c r="E52" s="3">
         <v>144784000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>146113000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>141224000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>135056000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>145802000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>149693000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>144608000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>145865000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>139200000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>130314000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>137412000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>134070000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8453000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9579000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9288000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8285000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6995000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6275000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5911000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6839000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6466000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6040000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6064000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7665000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7894000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5787000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6080000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6018000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6745000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6736000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7635000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7313000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8394000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>6722000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>6984000</v>
       </c>
-      <c r="AM52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5654,127 +5776,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>310382000</v>
+      </c>
+      <c r="E54" s="3">
         <v>317990000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>314409000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>303088000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>287366000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>295727000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>298989000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>287769000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>285577000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>276814000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>260252000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>269006000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>261500000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>252702000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>245600000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>253482000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>277658000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>292262000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>284579000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>285982000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>276832000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>275397000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>262496000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>254110000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>240781000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>249818000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>244646000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>238597000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>232819000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>220797000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>234451000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>231012000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>232294000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>235615000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>230825000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>226564000</v>
       </c>
-      <c r="AM54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5816,8 +5944,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5859,8 +5988,9 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5900,8 +6030,8 @@
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -5978,288 +6108,297 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E58" s="3">
         <v>540000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>77000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>104000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>146000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>137000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>127000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>152000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>147000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>370000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>113000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>29000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>751000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9539000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7270000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6820000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5992000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6636000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7059000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8017000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9456000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5947000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5038000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4890000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4632000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4608000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4208000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1698000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1640000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2063000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2400000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2350000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2404000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2387000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3784000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3747000</v>
       </c>
-      <c r="AM58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18552000</v>
+      </c>
+      <c r="E59" s="3">
         <v>21970000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21307000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18316000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14616000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17922000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16272000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15125000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13999000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10934000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8740000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9025000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6240000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6189000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5316000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5786000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7007000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6264000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5706000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5962000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6802000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7845000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7260000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7447000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8366000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6060000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6068000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6146000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6321000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5032000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4687000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4714000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4411000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4373000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AM59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19516000</v>
+      </c>
+      <c r="E60" s="3">
         <v>23880000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22751000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19874000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15404000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18834000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17781000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16116000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15168000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12536000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9307000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10576000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7879000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6335,180 +6474,186 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6927000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7142000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6363000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6803000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6440000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6645000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5575000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5570000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5401000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5958000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5361000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5303000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4988000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11278000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4026000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5698000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5318000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11848000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4772000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4867000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5105000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7321000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5916000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5915000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6336000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6403000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7086000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7144000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7299000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7455000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7306000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7422000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7403000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11530000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7142000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6786000</v>
       </c>
-      <c r="AM61" s="3">
-        <v>0</v>
-      </c>
       <c r="AN61" s="3">
         <v>0</v>
       </c>
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>281689000</v>
+      </c>
+      <c r="E62" s="3">
         <v>285180000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>283347000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>273448000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>261028000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>266700000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>269435000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>261610000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>260262000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>253162000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>241667000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>247336000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>242549000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>108000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -6517,26 +6662,26 @@
         <v>0</v>
       </c>
       <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
         <v>270000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>322000</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
       <c r="Z62" s="3">
         <v>0</v>
       </c>
       <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
         <v>679000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>724000</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6549,8 +6694,8 @@
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH62" s="3">
-        <v>0</v>
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI62" s="3">
         <v>0</v>
@@ -6573,8 +6718,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6692,8 +6840,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6811,8 +6962,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6930,127 +7084,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>308132000</v>
+      </c>
+      <c r="E66" s="3">
         <v>316202000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>312461000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>300125000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>282872000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>292179000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>292791000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>283296000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>280831000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>271656000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>256335000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>263215000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>255416000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>251301000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>242246000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>247893000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>269704000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>280743000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>272899000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>274250000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>266139000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>259821000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>245196000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>236516000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>220695000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>236362000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>229710000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>223754000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>219676000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>206931000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>222040000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>217674000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>218775000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>222246000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>218667000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>214442000</v>
       </c>
-      <c r="AM66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7092,8 +7252,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7211,8 +7372,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7330,8 +7494,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7342,16 +7509,16 @@
         <v>1068000</v>
       </c>
       <c r="F70" s="3">
+        <v>1068000</v>
+      </c>
+      <c r="G70" s="3">
         <v>1228000</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1507000</v>
       </c>
       <c r="H70" s="3">
         <v>1507000</v>
       </c>
       <c r="I70" s="3">
-        <v>1562000</v>
+        <v>1507000</v>
       </c>
       <c r="J70" s="3">
         <v>1562000</v>
@@ -7396,13 +7563,13 @@
         <v>1562000</v>
       </c>
       <c r="X70" s="3">
-        <v>1269000</v>
+        <v>1562000</v>
       </c>
       <c r="Y70" s="3">
         <v>1269000</v>
       </c>
       <c r="Z70" s="3">
-        <v>775000</v>
+        <v>1269000</v>
       </c>
       <c r="AA70" s="3">
         <v>775000</v>
@@ -7411,7 +7578,7 @@
         <v>775000</v>
       </c>
       <c r="AC70" s="3">
-        <v>0</v>
+        <v>775000</v>
       </c>
       <c r="AD70" s="3">
         <v>0</v>
@@ -7449,8 +7616,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7568,127 +7738,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8775000</v>
+      </c>
+      <c r="E72" s="3">
         <v>8366000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8360000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9870000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10447000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10627000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9977000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10317000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10110000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10243000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11163000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10325000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9806000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9825000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10839000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10718000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9312000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8880000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8857000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8739000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8758000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10699000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12032000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12995000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17112000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11744000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12835000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13293000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13004000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13989000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12031000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12613000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12455000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12225000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>11548000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>11558000</v>
       </c>
-      <c r="AM72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7806,8 +7982,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7925,8 +8104,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8044,127 +8226,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-795000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1142000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-920000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-79000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>894000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>58000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1658000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>82000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>470000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1087000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>80000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1991000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2192000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1792000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4027000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6392000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9957000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10118000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10170000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9131000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14307000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16031000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16819000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19311000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12681000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14936000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14843000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13143000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13866000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12411000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13338000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13519000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13369000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12158000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12122000</v>
       </c>
-      <c r="AM76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8282,251 +8470,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>621000</v>
+      </c>
+      <c r="E81" s="3">
         <v>215000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1309000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-349000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>63000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>892000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-132000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>428000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>92000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-698000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1064000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>759000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>177000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>36000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>580000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>941000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>516000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>228000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>658000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>97000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1501000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-790000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4029000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5375000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-946000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-374000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-444000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-775000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1938000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-496000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>164000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>214000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>483000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>10000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>341000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-290000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-366000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8568,127 +8765,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E83" s="3">
         <v>122000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>212000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>193000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>241000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>125000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>196000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>156000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>224000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>157000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>213000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>142000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>227000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>216000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>191000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>180000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>161000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>88000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>95000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>153000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>89000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>162000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>176000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1330000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>93000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>131000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>433000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>239000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>104000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>-195000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>184000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>164000</v>
       </c>
-      <c r="AJ83" s="3">
-        <v>0</v>
-      </c>
       <c r="AK83" s="3">
         <v>0</v>
       </c>
       <c r="AL83" s="3">
         <v>0</v>
       </c>
-      <c r="AM83" s="3" t="s">
-        <v>8</v>
+      <c r="AM83" s="3">
+        <v>0</v>
       </c>
       <c r="AN83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AO83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP83" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8806,8 +9007,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8925,8 +9129,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9044,8 +9251,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9163,8 +9373,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9282,127 +9495,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>499000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-154000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>369000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>341000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>158000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>400000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>683000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>892000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-392000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>410000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>361000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-587000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>61000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>229000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-608000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-402000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>241000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-581000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-14000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>553000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>22000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-570000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>76000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>133000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-425000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-109000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>94000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>281000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-67000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-247000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-23000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>378000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>666000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>72000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-54000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-22000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9444,127 +9663,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E91" s="3">
         <v>16000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-63000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-35000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-83000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-29000</v>
       </c>
       <c r="V91" s="3">
         <v>-29000</v>
       </c>
       <c r="W91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-23000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-63000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-14000</v>
       </c>
       <c r="AA91" s="3">
         <v>-14000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9682,8 +9905,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9801,127 +10027,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2955000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2483000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4768000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2518000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1199000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5536000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2392000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2682000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>115000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1087000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3215000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1577000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-171000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4540000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3751000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5530000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2585000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>4147000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4969000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2442000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-993000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2863000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1348000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>459000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3121000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1501000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-5067000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2899000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1326000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9963,110 +10195,111 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E96" s="3">
         <v>77000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>81000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>82000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>74000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>75000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>76000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>78000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>73000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>74000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>77000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>78000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>72000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-74000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-75000</v>
       </c>
       <c r="R96" s="3">
         <v>-75000</v>
       </c>
       <c r="S96" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-70000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-72000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-74000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-76000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-74000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-75000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-77000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-69000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-141000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-69000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
@@ -10082,8 +10315,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10201,8 +10437,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10320,8 +10559,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10439,361 +10681,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1494000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3052000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8942000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2228000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2549000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1583000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3364000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4945000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2387000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>470000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3394000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2749000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3589000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1513000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1108000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1437000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2330000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1751000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3994000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4436000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1498000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5285000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>557000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2334000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>992000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4581000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3132000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>838000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-181000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>700000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-264000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1400000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2771000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1376000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>4923000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>2630000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>954000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-28000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>21000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-10000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>25000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-18000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>10000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>34000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-38000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-41000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>34000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-38000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-41000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-11000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-14000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>22000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>12000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>16000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-3000</v>
       </c>
       <c r="AG101" s="3">
         <v>-3000</v>
       </c>
       <c r="AH101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>5000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>6000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>11000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>8000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2558000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1142000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1353000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6793000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1200000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2615000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-105000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-992000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2284000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2135000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1587000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2674000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>742000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>301000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-970000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-604000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>525000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-506000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1126000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>669000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2401000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>320000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1992000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5886000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-263000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>265000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>660000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-308000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2056000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>742000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1277000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>259000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>533000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-593000</v>
       </c>
     </row>
